--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:R92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +571,6 @@
       <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>CJKT3151335</t>
@@ -651,7 +650,6 @@
       <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>CJTZ3113454</t>
@@ -731,7 +729,6 @@
       <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CJMY3090389</t>
@@ -811,7 +808,6 @@
       <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>CJTZ3091878</t>
@@ -891,7 +887,6 @@
       <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CJLY3083517</t>
@@ -971,7 +966,6 @@
       <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CJWO3078837</t>
@@ -1051,7 +1045,6 @@
       <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CJTZ3077271</t>
@@ -1131,7 +1124,6 @@
       <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CJTZ3071585</t>
@@ -1211,7 +1203,6 @@
       <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CJWL3066864</t>
@@ -1291,7 +1282,6 @@
       <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CJTZ3067953</t>
@@ -1371,7 +1361,6 @@
       <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>CJKT3059304</t>
@@ -1451,7 +1440,6 @@
       <c r="N13" t="n">
         <v>1</v>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CJTZ3061309</t>
@@ -1531,7 +1519,6 @@
       <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CJTZ3057756</t>
@@ -1611,7 +1598,6 @@
       <c r="N15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CJQB3057928</t>
@@ -1691,7 +1677,6 @@
       <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CJTZ3055387</t>
@@ -1771,7 +1756,6 @@
       <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CJLT3048464</t>
@@ -1851,7 +1835,6 @@
       <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CJDK3015677</t>
@@ -1931,7 +1914,6 @@
       <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CJQB3009764</t>
@@ -2011,7 +1993,6 @@
       <c r="N20" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CJKT3009929</t>
@@ -2091,7 +2072,6 @@
       <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CJWY2995765</t>
@@ -2171,7 +2151,6 @@
       <c r="N22" t="n">
         <v>1</v>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CJJS2994644</t>
@@ -2251,7 +2230,6 @@
       <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>CJQB2994598</t>
@@ -2331,7 +2309,6 @@
       <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CJTZ2983407</t>
@@ -2411,7 +2388,6 @@
       <c r="N25" t="n">
         <v>1</v>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>CJLY2977859</t>
@@ -2491,7 +2467,6 @@
       <c r="N26" t="n">
         <v>1</v>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>CJTZ2977891</t>
@@ -2571,7 +2546,6 @@
       <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CJTZ2975608</t>
@@ -2651,7 +2625,6 @@
       <c r="N28" t="n">
         <v>1</v>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>CJTZ2974582</t>
@@ -2731,7 +2704,6 @@
       <c r="N29" t="n">
         <v>1</v>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CJTZ2974745</t>
@@ -2811,7 +2783,6 @@
       <c r="N30" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>CJTZ2972533</t>
@@ -2891,7 +2862,6 @@
       <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>CJMY2970588</t>
@@ -2971,7 +2941,6 @@
       <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>CJLT2962050</t>
@@ -3051,7 +3020,6 @@
       <c r="N33" t="n">
         <v>1</v>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>CJWL2962205</t>
@@ -3131,7 +3099,6 @@
       <c r="N34" t="n">
         <v>1</v>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>CJLY2960883</t>
@@ -3211,7 +3178,6 @@
       <c r="N35" t="n">
         <v>1</v>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>CJTZ2959166</t>
@@ -3291,7 +3257,6 @@
       <c r="N36" t="n">
         <v>1</v>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>CJLY2959189</t>
@@ -3371,7 +3336,6 @@
       <c r="N37" t="n">
         <v>1</v>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>CJWL2959133</t>
@@ -3451,7 +3415,6 @@
       <c r="N38" t="n">
         <v>1</v>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>CJWL2959120</t>
@@ -3531,7 +3494,6 @@
       <c r="N39" t="n">
         <v>1</v>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>CJLY2956614</t>
@@ -3611,7 +3573,6 @@
       <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>CJLT2956851</t>
@@ -3691,7 +3652,6 @@
       <c r="N41" t="n">
         <v>1</v>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>CJTZ2954056</t>
@@ -3771,7 +3731,6 @@
       <c r="N42" t="n">
         <v>1</v>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>CJWL2954034</t>
@@ -3851,7 +3810,6 @@
       <c r="N43" t="n">
         <v>1</v>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>CJLY2952354</t>
@@ -3931,7 +3889,6 @@
       <c r="N44" t="n">
         <v>1</v>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>CJWL2950701</t>
@@ -4011,7 +3968,6 @@
       <c r="N45" t="n">
         <v>1</v>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>CJQZ2950661</t>
@@ -4091,7 +4047,6 @@
       <c r="N46" t="n">
         <v>1</v>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>CJWL2950479</t>
@@ -4171,7 +4126,6 @@
       <c r="N47" t="n">
         <v>1</v>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>CJWL2949270</t>
@@ -4251,7 +4205,6 @@
       <c r="N48" t="n">
         <v>1</v>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>CJTZ2949455</t>
@@ -4331,7 +4284,6 @@
       <c r="N49" t="n">
         <v>1</v>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>CJTZ2949439</t>
@@ -4411,7 +4363,6 @@
       <c r="N50" t="n">
         <v>1</v>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>CJLY2949812</t>
@@ -4491,7 +4442,6 @@
       <c r="N51" t="n">
         <v>1</v>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>CJKT2949638</t>
@@ -4571,7 +4521,6 @@
       <c r="N52" t="n">
         <v>1</v>
       </c>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>CJLY2950046</t>
@@ -4651,7 +4600,6 @@
       <c r="N53" t="n">
         <v>1</v>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>CJQZ2950122</t>
@@ -4731,7 +4679,6 @@
       <c r="N54" t="n">
         <v>1</v>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>CJLY2949916</t>
@@ -4811,7 +4758,6 @@
       <c r="N55" t="n">
         <v>1</v>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>CJKT2950130</t>
@@ -4891,7 +4837,6 @@
       <c r="N56" t="n">
         <v>1</v>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>CJLY2948751</t>
@@ -4971,7 +4916,6 @@
       <c r="N57" t="n">
         <v>1</v>
       </c>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>CJKT2939320</t>
@@ -5051,7 +4995,6 @@
       <c r="N58" t="n">
         <v>1</v>
       </c>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>CJWL2939272</t>
@@ -5131,7 +5074,6 @@
       <c r="N59" t="n">
         <v>1</v>
       </c>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>CJJK2935423</t>
@@ -5211,7 +5153,6 @@
       <c r="N60" t="n">
         <v>1</v>
       </c>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>CJTZ2935345</t>
@@ -5291,7 +5232,6 @@
       <c r="N61" t="n">
         <v>1</v>
       </c>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>CJLY2934373</t>
@@ -5371,7 +5311,6 @@
       <c r="N62" t="n">
         <v>1</v>
       </c>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>CJWL2934898</t>
@@ -5451,7 +5390,6 @@
       <c r="N63" t="n">
         <v>1</v>
       </c>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>CJLT2934052</t>
@@ -5531,7 +5469,6 @@
       <c r="N64" t="n">
         <v>1</v>
       </c>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>CJWL2935395</t>
@@ -5611,7 +5548,6 @@
       <c r="N65" t="n">
         <v>1</v>
       </c>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>CJLY2935356</t>
@@ -5691,7 +5627,6 @@
       <c r="N66" t="n">
         <v>1</v>
       </c>
-      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>CJTZ2935432</t>
@@ -5771,7 +5706,6 @@
       <c r="N67" t="n">
         <v>1</v>
       </c>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>CJTZ2935441</t>
@@ -5851,7 +5785,6 @@
       <c r="N68" t="n">
         <v>1</v>
       </c>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>CJQZ2935408</t>
@@ -5931,7 +5864,6 @@
       <c r="N69" t="n">
         <v>1</v>
       </c>
-      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>CJKT2934384</t>
@@ -6011,7 +5943,6 @@
       <c r="N70" t="n">
         <v>1</v>
       </c>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>CJWS2930927</t>
@@ -6091,7 +6022,6 @@
       <c r="N71" t="n">
         <v>1</v>
       </c>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>CJKT2928545</t>
@@ -6105,6 +6035,1686 @@
       <c r="R71" t="inlineStr">
         <is>
           <t>2064585550960050178</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>z29d7djizwmm5v7321bqb71y</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Grey Grid Collision Black Sleeveless Waist Cinched A-line Short Suit Dress</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/763ec58e-2fc0-4216-93c6-cf5e94ff3430.png,https://cf.cjdropshipping.com/46e7183b-5954-4096-868a-83c7736595ce.png</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>60</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Step into sophistication with the Grey Grid Collision Black Sleeveless Waist Cinched A-line Short Suit Dress. Designed to flatter all body types, this modern piece combines a chic silhouette with stylish detailing. Perfect for any occasion, it effortlessly enhances your confidence and makes a bold statement wherever you go.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>[['Gray-S', 'CJLY292811301AZ'], ['Gray-M', 'CJLY292811302BY'], ['Gray-L', 'CJLY292811303CX'], ['Gray-Xl', 'CJLY292811304DW'], ['Gray-2xl', 'CJLY292811305EV']]</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>243</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>CJLY2928113</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>2064529979171561473</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>7a3h4yva09xokui0xb9whohz</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Gray Half-zip Waist-cinching Pleated Hoodie Dress</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/0cfcab34-92fe-46af-945f-467cc909fec6.jpg,https://cf.cjdropshipping.com/19cb9f52-4b04-44d0-b670-b6afdd9846b3.jpg,https://oss-cf.cjdropshipping.com/product/2026/07/17/08/5cfce949-887d-4176-9a1e-12e2539fe938.jpg,https://oss-cf.cjdropshipping.com/product/2026/07/17/08/84fb5b07-b394-4cea-8bea-b2bb6895146d.jpg</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>72</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Experience comfort and style with our Gray Half-zip Waist-cinching Pleated Hoodie Dress. This versatile piece features a flattering silhouette, adjustable waist for a customized fit, and pleated detailing for added flair. Perfect for casual outings or lounging at home, it combines practicality with fashion effortlessly. Upgrade your wardrobe today!</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>[['Gray-S', 'CJLY292824201AZ'], ['Gray-M', 'CJLY292824202BY'], ['Gray-L', 'CJLY292824203CX'], ['Gray-XL', 'CJLY292824204DW'], ['Gray-XXL', 'CJLY292824205EV'], ['Light Khaki-S', 'CJLY292824206FU'], ['Light Khaki-M', 'CJLY292824207GT'], ['Light Khaki-L', 'CJLY292824208HS'], ['Light Khaki-XL', 'CJLY292824209IR'], ['Light Khaki-XXL', 'CJLY292824210JQ'], ['Pink-S', 'CJLY292824211KP'], ['Pink-M', 'CJLY292824212LO'], ['Pink-L', 'CJLY292824213MN'], ['Pink-XL', 'CJLY292824214NM'], ['Pink-XXL', 'CJLY292824215OL']]</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>477</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>CJLY2928242</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>2064541723226324993</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>03llnq6gopdlp4eytgviscuu</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Women's Solid Color Lapel Zip Pullover Sweater, Loose 3D Casual Top For Autumn</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/3836e342-893b-4d9d-b32c-b50f806c438b.jpg,https://cf.cjdropshipping.com/8c09029a-3d57-496f-8b7f-7a6d0a13b6e3.jpg,https://cf.cjdropshipping.com/a138394b-681f-4bff-90a9-df49b002280b.jpg,https://cf.cjdropshipping.com/e4ea24dc-554c-4558-b420-100a6f42289a.jpg,https://cf.cjdropshipping.com/2abd05cf-a8f7-4b4e-9b44-18ce9e952a46.jpg,https://cf.cjdropshipping.com/0c10f83a-bce8-438b-bbe7-43aba62c047e.jpg,https://cf.cjdropshipping.com/72e66f42-96ac-42b2-9cd7-5ee9e6b7bc9a.jpg,https://cf.cjdropshipping.com/86d4d04f-0cf5-4656-b1f5-f638da9d06dd.jpg,https://cf.cjdropshipping.com/67096893-bfa5-4171-aac1-c18aee2a9684.jpg,https://cf.cjdropshipping.com/d3fbcb2b-975a-4760-8bea-48df25e2d9d6.jpg</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Stay cozy and stylish this autumn with our Women’s Solid Color Lapel Zip Pullover Sweater. This loose-fitting, 3D casual top offers unmatched comfort and versatility. Perfect for layering or wearing solo, it effortlessly complements your wardrobe, making it an essential piece for chilly days. Embrace warmth while looking fabulous!</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Sweaters</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>2</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>[['Sky Blue-S', 'CJMY292781301AZ'], ['Sky Blue-M', 'CJMY292781302BY'], ['Sky Blue-L', 'CJMY292781303CX'], ['Sky Blue-XL', 'CJMY292781304DW'], ['Sky Blue-XXL', 'CJMY292781305EV'], ['Sky Blue-XXXL', 'CJMY292781306FU'], ['OffWhite-S', 'CJMY292781307GT'], ['OffWhite-M', 'CJMY292781308HS'], ['OffWhite-L', 'CJMY292781309IR'], ['OffWhite-XL', 'CJMY292781310JQ'], ['OffWhite-XXL', 'CJMY292781311KP'], ['OffWhite-XXXL', 'CJMY292781312LO'], ['Army Green-S', 'CJMY292781313MN'], ['Army Green-M', 'CJMY292781314NM'], ['Army Green-L', 'CJMY292781315OL'], ['Army Green-XL', 'CJMY292781316PK'], ['Army Green-XXL', 'CJMY292781317QJ'], ['Army Green-XXXL', 'CJMY292781318RI'], ['Light Green-S', 'CJMY292781319SH'], ['Light Green-M', 'CJMY292781320TG'], ['Light Green-L', 'CJMY292781321UF'], ['Light Green-XL', 'CJMY292781322VE'], ['Light Green-XXL', 'CJMY292781323WD'], ['Light Green-XXXL', 'CJMY292781324XC'], ['Black-S', 'CJMY292781325YB'], ['Black-M', 'CJMY292781326ZA'], ['Black-L', 'CJMY292781327AZ'], ['Black-XL', 'CJMY292781328BY'], ['Black-XXL', 'CJMY292781329CX'], ['Black-XXXL', 'CJMY292781330DW'], ['Coffee-S', 'CJMY292781331EV'], ['Coffee-M', 'CJMY292781332FU'], ['Coffee-L', 'CJMY292781333GT'], ['Coffee-XL', 'CJMY292781334HS'], ['Coffee-XXL', 'CJMY292781335IR'], ['Coffee-XXXL', 'CJMY292781336JQ'], ['Grey-S', 'CJMY292781337KP'], ['Grey-M', 'CJMY292781338LO'], ['Grey-L', 'CJMY292781339MN'], ['Grey-XL', 'CJMY292781340NM'], ['Grey-XXL', 'CJMY292781341OL'], ['Grey-XXXL', 'CJMY292781342PK'], ['Pink-S', 'CJMY292781343QJ'], ['Pink-M', 'CJMY292781344RI'], ['Pink-L', 'CJMY292781345SH'], ['Pink-XL', 'CJMY292781346TG'], ['Pink-XXL', 'CJMY292781347UF'], ['Pink-XXXL', 'CJMY292781348VE'], ['Purple-S', 'CJMY292781349WD'], ['Purple-M', 'CJMY292781350XC'], ['Purple-L', 'CJMY292781351YB'], ['Purple-XL', 'CJMY292781352ZA'], ['Purple-XXL', 'CJMY292781353AZ'], ['Purple-XXXL', 'CJMY292781354BY'], ['Camel-S', 'CJMY292781355CX'], ['Camel-M', 'CJMY292781356DW'], ['Camel-L', 'CJMY292781357EV'], ['Camel-XL', 'CJMY292781358FU'], ['Camel-XXL', 'CJMY292781359GT'], ['Camel-XXXL', 'CJMY292781360HS']]</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>500</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>CJMY2927813</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2064344886167896065</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>j27dy61t82ntkyqyzzzbbby9</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Color Block Star Print Rib Collar Snap Button Longline Varsity Baseball Jacket</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/9650fffc-1527-4c81-997d-2933985d45a6.jpg,https://cf.cjdropshipping.com/ffb29f9a-1168-4dcc-880a-19187b18e9a5.jpg,https://cf.cjdropshipping.com/b8d2638b-39bf-4809-9b82-274e005346e2.jpg</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Step up your style with our Color Block Star Print Rib Collar Snap Button Longline Varsity Baseball Jacket. This trendy outerwear combines bold colors and a striking star print, perfect for making a statement. Its comfortable fit and sporty design effortlessly enhance any casual outfit, making it a must-have for fashion lovers.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>[['Green-S', 'CJTZ292747801AZ'], ['Green-M', 'CJTZ292747802BY'], ['Green-L', 'CJTZ292747803CX'], ['Green-Xl', 'CJTZ292747804DW'], ['Green-Xxl', 'CJTZ292747805EV']]</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>460</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>CJTZ2927478</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2064239006151770114</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>5livktiv2na72bknd4lra4hb</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Military Green Side Drawstring Loose Seven Quarter Sleeve T-shirt Short Skirt</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/4c3f6b8a-d4fc-4a65-8cd0-f49e0e1e7e0d.png,https://cf.cjdropshipping.com/2aade528-c014-4c9a-b270-46c7a35efcd4.png</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Discover ultimate comfort and style with our Military Green Side Drawstring Loose Seven Quarter Sleeve T-shirt Short Skirt. This versatile outfit combines casual elegance and practicality, perfect for any occasion. The adjustable drawstring allows for a customizable fit, while the trendy design ensures you remain fashionable and relaxed all day long.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>[['Green-S', 'CJLY292713301AZ'], ['Green-M', 'CJLY292713302BY'], ['Green-L', 'CJLY292713303CX'], ['Green-Xl', 'CJLY292713304DW'], ['Green-2xl', 'CJLY292713305EV']]</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>300</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>CJLY2927133</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2064205372002062338</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3m4x45jlxw0bsfam0p4qq9qc</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>One Shoulder Bubble Sleeve Black Lace Patchwork Red Short Dress</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/7669e640-8c49-4288-9e02-2ea86ae5a7ee.png,https://cf.cjdropshipping.com/63d3f1b4-4cd7-4a68-bb0e-0a7f85376263.png,https://cf.cjdropshipping.com/67d5449c-57e8-46d9-8b17-6fa6945c6c75.png</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>65</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Step into elegance with our One Shoulder Bubble Sleeve Black Lace Patchwork Red Short Dress. Featuring a chic asymmetrical design and luxurious lace detailing, this dress is perfect for making a statement at any event. Its vibrant hue and playful silhouette ensure all eyes will be on you. Embrace your bold side!</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>[['Red-S', 'CJLY292333101AZ'], ['Red-M', 'CJLY292333102BY'], ['Red-L', 'CJLY292333103CX'], ['Red-Xl', 'CJLY292333104DW'], ['Red-2xl', 'CJLY292333105EV']]</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>180</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>CJLY2923331</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2062838654164832257</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>xzrydi9v0x7amezkw0pq6kkz</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>V-neck Sleeveless Linen Top &amp; Drawstring Shorts Set</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/ba795410-1b1e-43ae-b0a9-fc04348c57df.png,https://cf.cjdropshipping.com/ed0b6104-fc19-4a68-8484-eda03f059360.png</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Embrace effortless style with our V-neck Sleeveless Linen Top &amp; Drawstring Shorts Set. Perfect for warm days, this breathable ensemble blends comfort and chic sophistication. The relaxed fit flatters every silhouette, while the versatile design allows for endless styling options. Stay cool and fashionable all summer long with this must-have outfit!</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>[['Offwhite-S', 'CJTZ292238801AZ'], ['Offwhite-M', 'CJTZ292238802BY'], ['Offwhite-L', 'CJTZ292238803CX'], ['Offwhite-XL', 'CJTZ292238804DW'], ['Offwhite-2XL', 'CJTZ292238805EV']]</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>251</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>CJTZ2922388</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>2062715584822607874</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ogky1xyn8espqa6i65vlmo39</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Polo Collar Yellow White Plaid Short Sleeve Romper</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/c18f716c-3bdf-4286-8511-d28a165d040d.png,https://cf.cjdropshipping.com/1159a077-f685-44af-b4b8-626b283439bb.png</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Introducing our Polo Collar Yellow White Plaid Short Sleeve Romper! This stylish romper combines comfort and flair, perfect for sunny outings. Its vibrant plaid pattern adds a playful touch, while the short sleeves keep you cool. Effortlessly chic, it’s an ideal choice for casual gatherings or lounging in style!</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Rompers</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>[['Yellow-S', 'CJLT292067001AZ'], ['Yellow-M', 'CJLT292067002BY'], ['Yellow-L', 'CJLT292067003CX'], ['Yellow-XL', 'CJLT292067004DW'], ['Yellow-2XL', 'CJLT292067005EV']]</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>312</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>CJLT2920670</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2062349378625118209</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>95t5znorpxw3ix1b6qhym87n</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Black Small High Neck Short Sleeved Slim Fit Professional Dress With Hip Hugging Design</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/c66d380c-9187-4bcf-973d-7a77f3f69e25.png,https://cf.cjdropshipping.com/12e8129a-1828-4503-a6b9-30c40931ad88.png</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Step into sophistication with our Black Small High Neck Short Sleeved Slim Fit Professional Dress. Featuring a stunning hip-hugging design, this dress effortlessly combines elegance with comfort. Perfect for the office or after hours, it accentuates your curves and makes a stylish statement. Elevate your wardrobe and shine on any occasion!</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJLY292186401AZ'], ['Black-M', 'CJLY292186402BY'], ['Black-L', 'CJLY292186403CX'], ['Black-Xl', 'CJLY292186404DW'], ['Black-2xl', 'CJLY292186405EV']]</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>186</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>CJLY2921864</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2062473459822686210</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>sgmbohhlfevpssmplm2szolv</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Mibai Collision Black Border Hanging Neck Linen Long Vacation Dress</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/f8c22b17-a8c5-40af-98f4-06fdef5907e9.png,https://cf.cjdropshipping.com/aacd7ef0-72e8-4468-b1eb-57d79a1dba42.png</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>60</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Discover the Mibai Collision Black Border Hanging Neck Linen Long Vacation Dress, perfect for your summer getaway. Crafted from breathable linen with a stylish design, it ensures comfort and elegance. The eye-catching black border adds sophistication, making it a must-have for effortless beach strolls or chic evening outings. Unleash your style!</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>[['Beige-S', 'CJLY292188501AZ'], ['Beige-M', 'CJLY292188502BY'], ['Beige-L', 'CJLY292188503CX'], ['Beige-Xl', 'CJLY292188504DW'], ['Beige-2xl', 'CJLY292188505EV']]</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>289</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>CJLY2921885</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>2062475444236754946</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>8pxvnwpj2ks0tc3w0y3w51x2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Hanging Neck Deep V-fold Split Vacation Long Dress</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/2932268b-c145-42e2-bc91-307ab719dbb0.png,https://cf.cjdropshipping.com/c2a53f58-3d26-4215-b0d8-6ba6eeeb085b.png</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Step into summer with our Hanging Neck Deep V-fold Split Vacation Long Dress. This stunning piece combines elegance and comfort, featuring a flattering deep V neckline and chic split design. Perfect for beach days or evening strolls, it effortlessly enhances your silhouette. Embrace style and confidence on your next getaway!</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>[['Haze Blue-S', 'CJLY292034901AZ'], ['Haze Blue-M', 'CJLY292034902BY'], ['Haze Blue-L', 'CJLY292034903CX'], ['Haze Blue-Xl', 'CJLY292034904DW'], ['Haze Blue-2xl', 'CJLY292034905EV']]</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>359</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>CJLY2920349</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>2062109525210071041</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>y308odbntu4jvtppzafvkgxc</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tibetan Blue And White Pleated Hem Long Sleeved Waist Cinching Short Dress</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/96a2356f-9041-456c-a22a-6a4ce8672b9e.png,https://cf.cjdropshipping.com/fd0674b6-136d-4b8a-9da1-471330e4f56f.png</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>77</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Unveil your elegance with the Tibetan Blue and White Pleated Hem Long Sleeved Dress. This stunning garment features a flattering waist-cinching design and delicate pleats, perfect for any occasion. Embrace your unique style and make a statement wherever you go. Comfortable and chic, this dress is a must-have addition to your wardrobe!</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>[['Navy blue-S', 'CJLY292036801AZ'], ['Navy blue-M', 'CJLY292036802BY'], ['Navy blue-L', 'CJLY292036803CX'], ['Navy blue-Xl', 'CJLY292036804DW'], ['Navy blue-2xl', 'CJLY292036805EV']]</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>420</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>CJLY2920368</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>2062112052915765250</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>pu2u1z1qspifztawzd53cbrf</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Cream &amp; Brown Trim Sleeveless Linen Top &amp; Shorts Set</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/ba263f77-287b-4354-a98e-981f110aa38b.png,https://cf.cjdropshipping.com/353f6415-525c-4eeb-8a93-b7609bc6f575.png</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>72</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Upgrade your summer wardrobe with our Cream &amp; Brown Trim Sleeveless Linen Top &amp; Shorts Set. This chic ensemble combines comfort and style, featuring breathable linen fabric and a flattering fit. Perfect for casual outings or beach days, it exudes effortless sophistication. Embrace warm weather with this must-have addition!</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>[['Cream Off White-S', 'CJTZ291903401AZ'], ['Cream Off White-M', 'CJTZ291903402BY'], ['Cream Off White-L', 'CJTZ291903403CX'], ['Cream Off White-XL', 'CJTZ291903404DW'], ['Cream Off White-2XL', 'CJTZ291903405EV']]</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>255</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>CJTZ2919034</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>2062006174329626626</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>fbzgusbk5zq34mktkybn34ps</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Contrast-color Neck-hanging Linen Set</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/7794ea88-fb99-43ac-9d65-49f0b2362a64.jpg,https://cf.cjdropshipping.com/0f2748a0-c695-4ee7-91c6-839b2246cafa.jpg</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Introducing the Contrast-color Neck-hanging Linen Set, a stylish blend of comfort and elegance. Crafted from high-quality linen, this unique design features vibrant contrast colors, perfect for adding flair to your wardrobe. Lightweight and breathable, it's ideal for any occasion. Upgrade your fashion game and make a statement today!</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJTZ291780801AZ'], ['White-M', 'CJTZ291780802BY'], ['White-L', 'CJTZ291780803CX'], ['White-XL', 'CJTZ291780804DW'], ['White-XXL', 'CJTZ291780805EV']]</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>250</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>CJTZ2917808</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>2061640561325268993</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>jaqz0ylsxh4w58eh9lwnowfh</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Black &amp; White Striped Halter Knit Romper</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/0ba5d596-7e6c-411c-8868-2f1948530e17.png,https://cf.cjdropshipping.com/61c6dce6-5b75-425d-aeda-ed02107c480f.png</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Step into style with our Black &amp; White Striped Halter Knit Romper! This chic piece features a trendy halter neck and comfortable fabric, perfect for casual outings or beach days. Its striking design adds flair to any wardrobe, ensuring you stand out effortlessly. Embrace fashion with this must-have romper!</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Rompers</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>[['Black  White-S', 'CJLT291788501AZ'], ['Black  White-M', 'CJLT291788502BY'], ['Black  White-L', 'CJLT291788503CX'], ['Black  White-XL', 'CJLT291788504DW'], ['Black  White-2XL', 'CJLT291788505EV']]</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>188</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>CJLT2917885</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>2061648721459896321</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>7j4rwuy0bdq871ovg28plal6</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Black And White Vertical Stripe V-neck Sleeveless Patchwork Ruffle Edge Dress</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/ad622daf-a6c7-414b-8d92-55996763fd0a.png,https://cf.cjdropshipping.com/e6923bde-5a47-4782-9655-a643c3875f15.png</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Step into style with the Black and White Vertical Stripe V-neck Sleeveless Patchwork Ruffle Edge Dress. This chic design combines playful ruffles with a flattering V-neck, perfect for any occasion. Its bold stripes and unique patchwork details ensure you stand out effortlessly, making it a must-have addition to your wardrobe.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJLY291734601AZ'], ['White-M', 'CJLY291734602BY'], ['White-L', 'CJLY291734603CX'], ['White-Xl', 'CJLY291734604DW'], ['White-2xl', 'CJLY291734605EV']]</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>183</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>CJLY2917346</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>2061371030694547458</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>m6prkynu8wxhv2p2ol58ozzb</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Green Short-sleeved Shirt And Wide-leg Pants Set</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://oss-cf.cjdropshipping.com/product/2026/06/15/02/f223fc63-da54-40b2-887b-760c61c7ad0e.jpg,https://oss-cf.cjdropshipping.com/product/2026/06/15/02/ae602353-b0e9-43f4-8452-c8eeaca1d72f.jpg</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Stylish and comfortable, the Green Short-sleeved Shirt and Wide-leg Pants Set is perfect for every occasion. This chic ensemble features breathable fabric and a relaxed fit, ensuring you stay fashionable while feeling at ease. Pair it with your favorite accessories for a stunning summer look that turns heads wherever you go!</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>2</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>[['Green-S', 'CJTZ291672301AZ'], ['Green-M', 'CJTZ291672302BY'], ['Green-L', 'CJTZ291672303CX'], ['Green-XL', 'CJTZ291672304DW'], ['Green-XXL', 'CJTZ291672305EV']]</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>393</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>CJTZ2916723</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>2061258621743681538</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>zfhvpr5sqztjccwf6cxz7jc7</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Lake Blue Cross Hanging Neck And Waist A-line Medium Length Dress</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/bb289e38-6682-4ba6-b4eb-470cb889f00a.png,https://cf.cjdropshipping.com/4e1cc535-7728-4774-8191-a61da59e9a5c.png</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>77</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Immerse yourself in effortless elegance with our Lake Blue Cross Hanging Neck and Waist A-Line Dress. This medium-length masterpiece combines style and comfort, featuring a stunning cross neckline and flattering A-line silhouette. Perfect for any occasion, this dress will make you feel confident and radiant. Embrace sophistication today!</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>[['Blue-S', 'CJLY291746101AZ'], ['Blue-M', 'CJLY291746102BY'], ['Blue-L', 'CJLY291746103CX'], ['Blue-Xl', 'CJLY291746104DW'], ['Blue-2xl', 'CJLY291746105EV']]</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>488</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>CJLY2917461</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>2061385035872821250</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>kb4m2t69f4gtdcglit611n93</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Half-zip Stand-up Collar Hoodie Dress</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/315f05a4-646c-43b7-846c-d5ee0864c549.jpg,https://cf.cjdropshipping.com/b24e3622-8088-439c-b8e3-b5787300b55d.jpg</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Upgrade your casual wardrobe with our Half-zip Stand-up Collar Hoodie Dress. This chic and versatile piece combines comfort and style, perfect for any occasion. Featuring a cozy hood and adjustable zipper, it offers an effortless look. Pair it with sneakers or boots for a trendy outfit you’ll love wearing!</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>[['Brown-S', 'CJLY291687901AZ'], ['Brown-M', 'CJLY291687902BY'], ['Brown-L', 'CJLY291687903CX'], ['Brown-XL', 'CJLY291687904DW'], ['Brown-XXL', 'CJLY291687905EV']]</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>450</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>CJLY2916879</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>2061286644921114626</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>3wdwrs1sd7sujac38cb1a21j</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Black Satin Lace-Trim V-Neck Top &amp; Skirt Set</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/c5121122-947d-4a7d-ac7b-704c8cdb7e89.jpg,https://cf.cjdropshipping.com/85c00822-ad44-4446-b9a5-b8138ef5a644.png</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Introducing the Black Satin Lace-Trim V-Neck Top &amp; Skirt Set, a stunning ensemble designed for sophistication. The luxurious satin fabric flows gracefully, complemented by delicate lace trim for an exquisite touch. Perfect for any occasion, this set effortlessly combines elegance and comfort, ensuring you turn heads wherever you go.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJTZ291671201AZ'], ['Black-M', 'CJTZ291671202BY'], ['Black-L', 'CJTZ291671203CX'], ['Black-XL', 'CJTZ291671204DW'], ['Black-2XL', 'CJTZ291671205EV'], ['White-S', 'CJTZ291671206FU'], ['White-M', 'CJTZ291671207GT'], ['White-L', 'CJTZ291671208HS'], ['White-XL', 'CJTZ291671209IR'], ['White-2XL', 'CJTZ291671210JQ']]</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>147</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>CJTZ2916712</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>2061254647762276354</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>m6yayuntu7y30vjvvbrja0ru</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Collared V-Neck Sleeveless Slit Midi Dress</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/8115ebe0-18dd-469b-97d0-398c79c65b61.png,https://cf.cjdropshipping.com/c8c93881-56c3-408a-8ea2-06f5e5f5adc3.png,https://cf.cjdropshipping.com/65ce6473-c1d4-4587-b63f-ed90cbf25589.png,https://cf.cjdropshipping.com/fc0a10af-b17e-4288-a19c-0e44aa5e6851.png,https://cf.cjdropshipping.com/2b274f63-8f2f-4c4f-b927-11b5ce8a5650.png</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Introducing our Collared V-Neck Sleeveless Slit Midi Dress—a perfect blend of sophistication and comfort. This stunning piece features a chic design with a flattering silhouette, ideal for any occasion. The stylish slit adds a touch of allure, ensuring you stand out effortlessly. Dress it up or down for a versatile look!</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJLY291680601AZ'], ['White-M', 'CJLY291680602BY'], ['White-L', 'CJLY291680603CX'], ['White-XL', 'CJLY291680604DW'], ['White-2XL', 'CJLY291680605EV'], ['Dusty Blue-S', 'CJLY291680606FU'], ['Dusty Blue-M', 'CJLY291680607GT'], ['Dusty Blue-L', 'CJLY291680608HS'], ['Dusty Blue-XL', 'CJLY291680609IR'], ['Dusty Blue-2XL', 'CJLY291680610JQ'], ['Charcoal Grey-S', 'CJLY291680611KP'], ['Charcoal Grey-M', 'CJLY291680612LO'], ['Charcoal Grey-L', 'CJLY291680613MN'], ['Charcoal Grey-XL', 'CJLY291680614NM'], ['Charcoal Grey-2XL', 'CJLY291680615OL'], ['Black-S', 'CJLY291680616PK'], ['Black-M', 'CJLY291680617QJ'], ['Black-L', 'CJLY291680618RI'], ['Black-XL', 'CJLY291680619SH'], ['Black-2XL', 'CJLY291680620TG'], ['Lavender Purple-S', 'CJLY291680621UF'], ['Lavender Purple-M', 'CJLY291680622VE'], ['Lavender Purple-L', 'CJLY291680623WD'], ['Lavender Purple-XL', 'CJLY291680624XC'], ['Lavender Purple-2XL', 'CJLY291680625YB']]</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>279</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>CJLY2916806</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>2061274080819957761</t>
         </is>
       </c>
     </row>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R92"/>
+  <dimension ref="A1:R161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6101,7 +6101,6 @@
       <c r="N72" t="n">
         <v>1</v>
       </c>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>CJLY2928113</t>
@@ -6181,7 +6180,6 @@
       <c r="N73" t="n">
         <v>1</v>
       </c>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>CJLY2928242</t>
@@ -6261,7 +6259,6 @@
       <c r="N74" t="n">
         <v>1</v>
       </c>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>CJMY2927813</t>
@@ -6341,7 +6338,6 @@
       <c r="N75" t="n">
         <v>1</v>
       </c>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>CJTZ2927478</t>
@@ -6421,7 +6417,6 @@
       <c r="N76" t="n">
         <v>1</v>
       </c>
-      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>CJLY2927133</t>
@@ -6501,7 +6496,6 @@
       <c r="N77" t="n">
         <v>1</v>
       </c>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>CJLY2923331</t>
@@ -6581,7 +6575,6 @@
       <c r="N78" t="n">
         <v>1</v>
       </c>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>CJTZ2922388</t>
@@ -6661,7 +6654,6 @@
       <c r="N79" t="n">
         <v>1</v>
       </c>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>CJLT2920670</t>
@@ -6741,7 +6733,6 @@
       <c r="N80" t="n">
         <v>1</v>
       </c>
-      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>CJLY2921864</t>
@@ -6821,7 +6812,6 @@
       <c r="N81" t="n">
         <v>1</v>
       </c>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>CJLY2921885</t>
@@ -6901,7 +6891,6 @@
       <c r="N82" t="n">
         <v>1</v>
       </c>
-      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>CJLY2920349</t>
@@ -6981,7 +6970,6 @@
       <c r="N83" t="n">
         <v>1</v>
       </c>
-      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>CJLY2920368</t>
@@ -7061,7 +7049,6 @@
       <c r="N84" t="n">
         <v>1</v>
       </c>
-      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>CJTZ2919034</t>
@@ -7141,7 +7128,6 @@
       <c r="N85" t="n">
         <v>1</v>
       </c>
-      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>CJTZ2917808</t>
@@ -7221,7 +7207,6 @@
       <c r="N86" t="n">
         <v>1</v>
       </c>
-      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>CJLT2917885</t>
@@ -7301,7 +7286,6 @@
       <c r="N87" t="n">
         <v>1</v>
       </c>
-      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>CJLY2917346</t>
@@ -7381,7 +7365,6 @@
       <c r="N88" t="n">
         <v>1</v>
       </c>
-      <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>CJTZ2916723</t>
@@ -7461,7 +7444,6 @@
       <c r="N89" t="n">
         <v>1</v>
       </c>
-      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>CJLY2917461</t>
@@ -7541,7 +7523,6 @@
       <c r="N90" t="n">
         <v>1</v>
       </c>
-      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>CJLY2916879</t>
@@ -7621,7 +7602,6 @@
       <c r="N91" t="n">
         <v>1</v>
       </c>
-      <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>CJTZ2916712</t>
@@ -7701,7 +7681,6 @@
       <c r="N92" t="n">
         <v>1</v>
       </c>
-      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>CJLY2916806</t>
@@ -7715,6 +7694,5479 @@
       <c r="R92" t="inlineStr">
         <is>
           <t>2061274080819957761</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>m0rzwav9fb1rc7kn1yda2w6i</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Women's Boho Paisley Print V-Neck Flare Sleeve Ruffle Hem Maxi Dress, Casual Loose Tie Waist Long Dress For Vacation &amp; Beach</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/d8bd09d5-d6bf-48df-ba93-bd5889f77554.jpg,https://cf.cjdropshipping.com/2936359a-247c-4356-870e-4e46110531f4.jpg,https://cf.cjdropshipping.com/d4fe28d6-23c6-43a8-8370-bede28d42afe.jpg,https://cf.cjdropshipping.com/a1601061-71d9-47b8-8c20-99627a153213.jpg,https://cf.cjdropshipping.com/23161dea-36fa-467b-8a2b-28310081c782.jpg,https://cf.cjdropshipping.com/76aecf4f-390c-4d80-91b6-ab287d28edad.jpg,https://cf.cjdropshipping.com/6a3a86e0-f87a-40e8-b037-e26c2c084a96.jpg</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Embrace effortless style with our Women's Boho Paisley Print V-Neck Flare Sleeve Ruffle Hem Maxi Dress. Perfect for vacations or beach outings, this casual dress features a loose fit and a chic tie waist that flatters every silhouette. Enjoy comfort and elegance while soaking up the sun in this stunning piece!</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>8</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>[['Red-S', 'CJLY291665301AZ'], ['Red-M', 'CJLY291665302BY'], ['Red-L', 'CJLY291665303CX'], ['Red-XL', 'CJLY291665304DW'], ['Red-XXL', 'CJLY291665305EV'], ['Red-3XL', 'CJLY291665306FU'], ['Red-4XL', 'CJLY291665307GT'], ['Red-5XL', 'CJLY291665308HS'], ['Green-S', 'CJLY291665309IR'], ['Green-M', 'CJLY291665310JQ'], ['Green-L', 'CJLY291665311KP'], ['Green-XL', 'CJLY291665312LO'], ['Green-XXL', 'CJLY291665313MN'], ['Green-3XL', 'CJLY291665314NM'], ['Green-4XL', 'CJLY291665315OL'], ['Green-5XL', 'CJLY291665316PK'], ['Blue-S', 'CJLY291665317QJ'], ['Blue-M', 'CJLY291665318RI'], ['Blue-L', 'CJLY291665319SH'], ['Blue-XL', 'CJLY291665320TG'], ['Blue-XXL', 'CJLY291665321UF'], ['Blue-3XL', 'CJLY291665322VE'], ['Blue-4XL', 'CJLY291665323WD'], ['Blue-5XL', 'CJLY291665324XC'], ['Purple-S', 'CJLY291665325YB'], ['Purple-M', 'CJLY291665326ZA'], ['Purple-L', 'CJLY291665327AZ'], ['Purple-XL', 'CJLY291665328BY'], ['Purple-XXL', 'CJLY291665329CX'], ['Purple-3XL', 'CJLY291665330DW'], ['Purple-4XL', 'CJLY291665331EV'], ['Purple-5XL', 'CJLY291665332FU'], ['Grey-S', 'CJLY291665333GT'], ['Grey-M', 'CJLY291665334HS'], ['Grey-L', 'CJLY291665335IR'], ['Grey-XL', 'CJLY291665336JQ'], ['Grey-XXL', 'CJLY291665337KP'], ['Grey-3XL', 'CJLY291665338LO'], ['Grey-4XL', 'CJLY291665339MN'], ['Grey-5XL', 'CJLY291665340NM'], ['Orange-S', 'CJLY291665341OL'], ['Orange-M', 'CJLY291665342PK'], ['Orange-L', 'CJLY291665343QJ'], ['Orange-XL', 'CJLY291665344RI'], ['Orange-XXL', 'CJLY291665345SH'], ['Orange-3XL', 'CJLY291665346TG'], ['Orange-4XL', 'CJLY291665347UF'], ['Orange-5XL', 'CJLY291665348VE']]</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>530</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>CJLY2916653</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>2061029371940233218</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>yikrckgjyxfmih020fp7i5wl</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Half-zip Ruffled Hoodie Dress</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/de414b7e-8d38-4086-b252-bba337a34db0.jpg,https://cf.cjdropshipping.com/1d74ef4a-de17-4295-a049-808eb2f6c7c8.jpg</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>72</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Discover ultimate comfort with our Half-zip Ruffled Hoodie Dress. Designed for versatility, this stylish piece merges casual elegance with a cozy feel. The unique ruffled hem adds a playful touch, perfect for any occasion. Embrace effortless chic and redefine your wardrobe with this must-have dress that guarantees compliments!</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>3</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>[['Pink-S', 'CJLY291555201AZ'], ['Pink-M', 'CJLY291555202BY'], ['Pink-L', 'CJLY291555203CX'], ['Pink-XL', 'CJLY291555204DW'], ['Pink-XXL', 'CJLY291555205EV']]</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>612</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>CJLY2915552</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>2060564195006144513</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>9gso1f60agahfnaqntxxe66x</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Printed Satin V-Neck Top &amp; Wide-Leg Pants Set</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/84cad764-6e3c-486f-abac-f381e6f1818a.png,https://cf.cjdropshipping.com/45b09a92-345c-4120-9a30-b7306e4dab13.png,https://cf.cjdropshipping.com/c5132cb1-27b1-432c-a25a-37cf49e07b19.png,https://cf.cjdropshipping.com/3eb67557-91ef-49fa-a901-4d28ac357332.png</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>60</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Transform your wardrobe with our Printed Satin V-Neck Top &amp; Wide-Leg Pants Set. Crafted from luxurious satin, this ensemble offers a perfect blend of comfort and style. The flowing wide legs create movement, while the chic V-neck adds femininity. Perfect for any occasion, dress it up or down effortlessly!</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>[['Green-S', 'CJTZ291491401AZ'], ['Green-M', 'CJTZ291491402BY'], ['Green-L', 'CJTZ291491403CX'], ['Green-XL', 'CJTZ291491404DW'], ['Green-2XL', 'CJTZ291491405EV'], ['Black-S', 'CJTZ291491406FU'], ['Black-M', 'CJTZ291491407GT'], ['Black-L', 'CJTZ291491408HS'], ['Black-XL', 'CJTZ291491409IR'], ['Black-2XL', 'CJTZ291491410JQ'], ['Caramel Brown-S', 'CJTZ291491411KP'], ['Caramel Brown-M', 'CJTZ291491412LO'], ['Caramel Brown-L', 'CJTZ291491413MN'], ['Caramel Brown-XL', 'CJTZ291491414NM'], ['Caramel Brown-2XL', 'CJTZ291491415OL'], ['Bright Red-S', 'CJTZ291491416PK'], ['Bright Red-M', 'CJTZ291491417QJ'], ['Bright Red-L', 'CJTZ291491418RI'], ['Bright Red-XL', 'CJTZ291491419SH'], ['Bright Red-2XL', 'CJTZ291491420TG']]</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>530</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>CJTZ2914914</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>2060269934427693057</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>aajlbx2gbw45shoxt9zsfo3b</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>V-Neck Sleeveless Linen-Blend Top &amp; Black-and-White Striped Lantern Pants Set</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/e8a8ae5e-c839-4d08-b1b3-ef434b56d930.png,https://cf.cjdropshipping.com/092b0441-7f00-41d3-a3cd-90a9cba21b45.png,https://cf.cjdropshipping.com/2b389def-5846-4371-8986-9001143f7e2e.png</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Elevate your wardrobe with our V-Neck Sleeveless Linen-Blend Top and Black-and-White Striped Lantern Pants Set. This chic ensemble seamlessly combines comfort and style, perfect for any occasion. Lightweight fabric ensures breathability, while the striking stripes add a dash of flair. Step out confidently and turn heads effortlessly. Your new favorite look awaits!</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>[['Blue-S', 'CJTZ291392501AZ'], ['Blue-M', 'CJTZ291392502BY'], ['Blue-L', 'CJTZ291392503CX'], ['Blue-XL', 'CJTZ291392504DW'], ['Blue-2XL', 'CJTZ291392505EV'], ['Off White-S', 'CJTZ291392506FU'], ['Off White-M', 'CJTZ291392507GT'], ['Off White-L', 'CJTZ291392508HS'], ['Off White-XL', 'CJTZ291392509IR'], ['Off White-2XL', 'CJTZ291392510JQ'], ['Terracotta-S', 'CJTZ291392511KP'], ['Terracotta-M', 'CJTZ291392512LO'], ['Terracotta-L', 'CJTZ291392513MN'], ['Terracotta-XL', 'CJTZ291392514NM'], ['Terracotta-2XL', 'CJTZ291392515OL']]</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>332</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>CJTZ2913925</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>2060186333388263426</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>spahbp40uavt0lkbhe66j0lp</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Hot Selling Women's Solid Color Smocked Wide Leg Pants With Elastic Waist</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/509bbd1e-5946-408c-a209-1689df78239c.jpg,https://cf.cjdropshipping.com/2dfef6af-3145-47f1-9736-341af8561099.jpg,https://cf.cjdropshipping.com/a0fa6c11-8409-451c-bc53-029caa3d1556.jpg,https://cf.cjdropshipping.com/8beb327b-f96d-4612-a377-c1d25926fc91.jpg,https://cf.cjdropshipping.com/05c54439-4fcd-4c79-aa48-0630ec9bb8da.jpg,https://cf.cjdropshipping.com/6606f673-d03b-4d6d-b503-bb4dd809b4a0.jpg,https://cf.cjdropshipping.com/5f867312-d678-4c88-b0e7-e56073f729a2.jpg,https://cf.cjdropshipping.com/dcb95a7d-b919-4a32-8d93-02884e86b921.jpg,https://cf.cjdropshipping.com/087c9460-49e3-4559-9adf-1ec1eb06c00d.jpg,https://cf.cjdropshipping.com/2e7fbdab-d968-4ac4-8c9d-359a5933bca0.jpg,https://cf.cjdropshipping.com/796f1592-e17d-4b6d-a06e-0711f2d4497d.jpg,https://cf.cjdropshipping.com/0683fd68-6554-498b-8a9f-269537b42e29.jpg,https://cf.cjdropshipping.com/d8f8cc1f-4879-46ab-a001-f2d0a0e86b46.jpg,https://cf.cjdropshipping.com/bcfd9a01-c0da-4245-b03f-6ef166ceb317.png,https://cf.cjdropshipping.com/72639e22-73db-4f0a-9972-cfecc02fca39.png</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Discover ultimate comfort with our Hot Selling Women's Solid Color Smocked Wide Leg Pants. Featuring an elastic waistband for a relaxed fit, these stylish trousers cascade gracefully, making them perfect for any occasion. Versatile and chic, they effortlessly enhance your wardrobe while providing all-day ease. Embrace modern fashion with confidence!</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Bottoms , Wide Leg Pants</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>13</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJKT291394901AZ'], ['White-M', 'CJKT291394902BY'], ['White-L', 'CJKT291394903CX'], ['White-XL', 'CJKT291394904DW'], ['White-XXL', 'CJKT291394905EV'], ['Khaki-S', 'CJKT291394906FU'], ['Khaki-M', 'CJKT291394907GT'], ['Khaki-L', 'CJKT291394908HS'], ['Khaki-XL', 'CJKT291394909IR'], ['Khaki-XXL', 'CJKT291394910JQ'], ['Grey-S', 'CJKT291394911KP'], ['Grey-M', 'CJKT291394912LO'], ['Grey-L', 'CJKT291394913MN'], ['Grey-XL', 'CJKT291394914NM'], ['Grey-XXL', 'CJKT291394915OL'], ['Green-S', 'CJKT291394916PK'], ['Green-M', 'CJKT291394917QJ'], ['Green-L', 'CJKT291394918RI'], ['Green-XL', 'CJKT291394919SH'], ['Green-XXL', 'CJKT291394920TG'], ['Black-S', 'CJKT291394921UF'], ['Black-M', 'CJKT291394922VE'], ['Black-L', 'CJKT291394923WD'], ['Black-XL', 'CJKT291394924XC'], ['Black-XXL', 'CJKT291394925YB'], ['Purple-S', 'CJKT291394926ZA'], ['Purple-M', 'CJKT291394927AZ'], ['Purple-L', 'CJKT291394928BY'], ['Purple-XL', 'CJKT291394929CX'], ['Purple-XXL', 'CJKT291394930DW'], ['Navy Blue-S', 'CJKT291394931EV'], ['Navy Blue-M', 'CJKT291394932FU'], ['Navy Blue-L', 'CJKT291394933GT'], ['Navy Blue-XL', 'CJKT291394934HS'], ['Navy Blue-XXL', 'CJKT291394935IR'], ['Orange Red-S', 'CJKT291394936JQ'], ['Orange Red-M', 'CJKT291394937KP'], ['Orange Red-L', 'CJKT291394938LO'], ['Orange Red-XL', 'CJKT291394939MN'], ['Orange Red-XXL', 'CJKT291394940NM'], ['Magenta-S', 'CJKT291394941OL'], ['Magenta-M', 'CJKT291394942PK'], ['Magenta-L', 'CJKT291394943QJ'], ['Magenta-XL', 'CJKT291394944RI'], ['Magenta-XXL', 'CJKT291394945SH'], ['Neon Green-S', 'CJKT291394946TG'], ['Neon Green-M', 'CJKT291394947UF'], ['Neon Green-L', 'CJKT291394948VE'], ['Neon Green-XL', 'CJKT291394949WD'], ['Neon Green-XXL', 'CJKT291394950XC'], ['Peacock Blue-S', 'CJKT291394951YB'], ['Peacock Blue-M', 'CJKT291394952ZA'], ['Peacock Blue-L', 'CJKT291394953AZ'], ['Peacock Blue-XL', 'CJKT291394954BY'], ['Peacock Blue-XXL', 'CJKT291394955CX'], ['Pink-S', 'CJKT291394956DW'], ['Pink-M', 'CJKT291394957EV'], ['Pink-L', 'CJKT291394958FU'], ['Pink-XL', 'CJKT291394959GT'], ['Pink-XXL', 'CJKT291394960HS'], ['Apricot-S', 'CJKT291394961IR'], ['Apricot-M', 'CJKT291394962JQ'], ['Apricot-L', 'CJKT291394963KP'], ['Apricot-XL', 'CJKT291394964LO'], ['Apricot-XXL', 'CJKT291394965MN'], ['Emerald Green-S', 'CJKT291394966NM'], ['Emerald Green-M', 'CJKT291394967OL'], ['Emerald Green-L', 'CJKT291394968PK'], ['Emerald Green-XL', 'CJKT291394969QJ'], ['Emerald Green-XXL', 'CJKT291394970RI'], ['Light Brown-S', 'CJKT291394971SH'], ['Light Brown-M', 'CJKT291394972TG'], ['Light Brown-L', 'CJKT291394973UF'], ['Light Brown-XL', 'CJKT291394974VE'], ['Light Brown-XXL', 'CJKT291394975WD']]</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>300</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>1</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>CJKT2913949</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2060191892682362881</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cfm98tpvsiwwj1y25w6tk9ma</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Embroidered Floral Long-Sleeve Button-Down Blouse</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/fc2277b9-72ce-46c3-975d-3e6814e5a829.png,https://cf.cjdropshipping.com/d33e83bd-f7bf-4e26-a9b5-99acd350b6ac.png</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Introducing the Embroidered Floral Long-Sleeve Button-Down Blouse—your new wardrobe essential! This stunning piece combines delicate embroidery with a classic silhouette, offering both elegance and comfort. Perfect for any occasion, it pairs beautifully with jeans or skirts, adding a touch of femininity to every outfit. Unleash your style today!</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Blouses , Shirts</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>[['Off White-S', 'CJCS291397601AZ'], ['Off White-M', 'CJCS291397602BY'], ['Off White-L', 'CJCS291397603CX'], ['Off White-XL', 'CJCS291397604DW'], ['Off White-2XL', 'CJCS291397605EV'], ['Sky Blue-S', 'CJCS291397606FU'], ['Sky Blue-M', 'CJCS291397607GT'], ['Sky Blue-L', 'CJCS291397608HS'], ['Sky Blue-XL', 'CJCS291397609IR'], ['Sky Blue-2XL', 'CJCS291397610JQ']]</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>190</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>1</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>CJCS2913976</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>2060188611063107585</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0fz2wmudvqvqdvwc7eedy6fj</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Holiday V-neck Sleeveless Dress</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/c988a848-6322-4508-8b4f-073455ffb7c1.jpg,https://cf.cjdropshipping.com/0126957c-93dc-48be-94a0-ac9ae4fc5a2d.jpg</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Step into elegance with our Holiday V-neck Sleeveless Dress. This stunning piece features a flattering silhouette, perfect for festive gatherings or summer soirées. Crafted from breathable fabric, it ensures comfort while exuding sophistication. Pair it with your favorite accessories to create a memorable look that’s sure to turn heads.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>[['Green-S', 'CJLY291325101AZ'], ['Green-M', 'CJLY291325102BY'], ['Green-L', 'CJLY291325103CX'], ['Green-XL', 'CJLY291325104DW'], ['Green-XXL', 'CJLY291325105EV']]</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>176</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>CJLY2913251</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>2059906774316900354</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>bdm2w6mg0vp32rc8yotkukaj</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Women Spring Summer Minimalist Elegant Dress, Solid Color V Neck Sleeveless Dress With Metal Buttons</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/44d4e8ac-8d31-4a1a-b797-a2b3e04156f7.jpg,https://cf.cjdropshipping.com/1d52fed5-6084-45fc-8080-fc4c15dd79b3.jpg,https://cf.cjdropshipping.com/6c5b5b7f-ed85-420a-a585-3a35936be2c4.jpg,https://cf.cjdropshipping.com/167166ff-0888-4974-be0e-942b36a6907d.jpg,https://cf.cjdropshipping.com/b1d138db-7f1b-4ad8-8134-60d9b78eb735.jpg,https://cf.cjdropshipping.com/fe9b0c00-db10-41e5-93e3-f9422c141c64.jpg,https://cf.cjdropshipping.com/77479d79-017d-4bc5-aad6-aa7041936a36.jpg,https://cf.cjdropshipping.com/79cb7688-96a9-411c-9cda-e3d6ac29ea14.png,https://cf.cjdropshipping.com/41f81323-85d2-4b0b-9eac-435b4c12c995.jpg,https://cf.cjdropshipping.com/6324c4d7-342a-4cbc-a964-4007f5df1713.jpg,https://cf.cjdropshipping.com/2c9e7adf-9e81-4d2e-98c9-2f32e0827029.jpg,https://cf.cjdropshipping.com/fffde055-6b28-4ce1-b416-66586f57ad01.jpg</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Embrace effortless style with our Women Spring Summer Minimalist Elegant Dress. This sleeveless design features a chic V-neck and eye-catching metal buttons, perfect for any occasion. Crafted from breathable fabric, it exudes sophistication while ensuring comfort. Versatile and timeless, this solid color piece is a must-have addition to your wardrobe!</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>7</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJLY291378201AZ'], ['Black-M', 'CJLY291378202BY'], ['Black-L', 'CJLY291378203CX'], ['Black-XL', 'CJLY291378204DW'], ['Black-XXL', 'CJLY291378205EV'], ['Black-1XL', 'CJLY291378206FU'], ['Black-2XL', 'CJLY291378207GT'], ['Black-3XL', 'CJLY291378208HS'], ['Black-4XL', 'CJLY291378209IR'], ['Black-5XL', 'CJLY291378210JQ'], ['Pink-S', 'CJLY291378211KP'], ['Pink-M', 'CJLY291378212LO'], ['Pink-L', 'CJLY291378213MN'], ['Pink-XL', 'CJLY291378214NM'], ['Pink-XXL', 'CJLY291378215OL'], ['Pink-1XL', 'CJLY291378216PK'], ['Pink-2XL', 'CJLY291378217QJ'], ['Pink-3XL', 'CJLY291378218RI'], ['Pink-4XL', 'CJLY291378219SH'], ['Pink-5XL', 'CJLY291378220TG'], ['White-S', 'CJLY291378221UF'], ['White-M', 'CJLY291378222VE'], ['White-L', 'CJLY291378223WD'], ['White-XL', 'CJLY291378224XC'], ['White-XXL', 'CJLY291378225YB'], ['White-1XL', 'CJLY291378226ZA'], ['White-2XL', 'CJLY291378227AZ'], ['White-3XL', 'CJLY291378228BY'], ['White-4XL', 'CJLY291378229CX'], ['White-5XL', 'CJLY291378230DW'], ['Green-S', 'CJLY291378231EV'], ['Green-M', 'CJLY291378232FU'], ['Green-L', 'CJLY291378233GT'], ['Green-XL', 'CJLY291378234HS'], ['Green-XXL', 'CJLY291378235IR'], ['Green-1XL', 'CJLY291378236JQ'], ['Green-2XL', 'CJLY291378237KP'], ['Green-3XL', 'CJLY291378238LO'], ['Green-4XL', 'CJLY291378239MN'], ['Green-5XL', 'CJLY291378240NM'], ['Orange-S', 'CJLY291378241OL'], ['Orange-M', 'CJLY291378242PK'], ['Orange-L', 'CJLY291378243QJ'], ['Orange-XL', 'CJLY291378244RI'], ['Orange-XXL', 'CJLY291378245SH'], ['Orange-1XL', 'CJLY291378246TG'], ['Orange-2XL', 'CJLY291378247UF'], ['Orange-3XL', 'CJLY291378248VE'], ['Orange-4XL', 'CJLY291378249WD'], ['Orange-5XL', 'CJLY291378250XC']]</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>260</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>CJLY2913782</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>2060023106452901889</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>yf788orlnoo8o66npbojjlac</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Plus Size Women's Boho Floral Print Spaghetti Strap Maxi Dress, High Waist V Neck Bohemian Long Dress</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/780195d9-f8dd-442e-9fe8-802b6f4e1a31.jpg,https://cf.cjdropshipping.com/f49b3e54-3338-4939-965e-1680623c35c3.jpg,https://cf.cjdropshipping.com/5f144fef-77c2-4f06-b735-136f2cbb54ac.jpg,https://cf.cjdropshipping.com/3da6004c-5a17-436b-ac0f-3ae722c9c5df.jpg,https://cf.cjdropshipping.com/6b34dee2-8310-4862-9ac3-193b897be68c.jpg,https://cf.cjdropshipping.com/cc0ed2b4-ce6b-468d-ba3c-7bce6e9d2fb2.jpg</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>36</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Embrace effortless elegance with our Plus Size Women's Boho Floral Print Spaghetti Strap Maxi Dress. Featuring a flattering high waist and V-neck design, this bohemian-inspired long dress flows beautifully and enhances your curves. Perfect for sunny days or casual outings, it promises comfort and style in one stunning piece.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>6</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>[['Wine Red-3XL', 'CJLY291375901AZ'], ['Wine Red-4XL', 'CJLY291375902BY'], ['Wine Red-5XL', 'CJLY291375903CX'], ['Yellow-3XL', 'CJLY291375904DW'], ['Yellow-4XL', 'CJLY291375905EV'], ['Yellow-5XL', 'CJLY291375906FU']]</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>360</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>CJLY2913759</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2060000952395161602</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>94sya0mwzi1utklx79l3achk</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Light Blue Vacation-Style Wrap Neck Wide-Leg Shorts Two-Piece Set</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://oss-cf.cjdropshipping.com/product/2026/06/09/04/9059dffd-7f53-4343-8cfc-43633b27bd54.jpg,https://oss-cf.cjdropshipping.com/product/2026/06/09/04/cb753fb8-fb8d-4b1d-bf31-d5f88390da27.jpg</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Experience summer bliss with the Light Blue Vacation-Style Wrap Neck Wide-Leg Shorts Two-Piece Set. This chic ensemble features a flattering wrap neckline and breezy wide-leg shorts, perfect for afternoons by the beach or casual outings. Enjoy comfort and style all season long while making unforgettable memories in this stunning outfit.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>[['Blue-S', 'CJTZ291285201AZ'], ['Blue-M', 'CJTZ291285202BY'], ['Blue-L', 'CJTZ291285203CX'], ['Blue-XL', 'CJTZ291285204DW'], ['Blue-XXL', 'CJTZ291285205EV']]</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>220</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>1</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>CJTZ2912852</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>2059867201891385346</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>evs4yhrddd39ghvoqfbyi5il</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hot New Summer Women's Elegant Maxi Tiered Dress</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/41dd54a1-323b-4c34-8cda-5af6f27bb0c4.jpg,https://cf.cjdropshipping.com/bcec351e-a219-416d-a468-59533727e529.jpg,https://cf.cjdropshipping.com/8a6d2b91-aec4-4dac-bb31-ec6bdb348568.jpg,https://cf.cjdropshipping.com/5e630999-5386-4d86-960e-22264ac6d62c.png,https://cf.cjdropshipping.com/beb039bc-db83-4cf2-a5e1-e7112ce6c63f.jpg,https://cf.cjdropshipping.com/f33ee451-e4d8-4506-802a-6b19f3dff0e8.jpg,https://cf.cjdropshipping.com/2034de00-7231-4eac-a211-9a14edfa7019.jpg,https://cf.cjdropshipping.com/dba87694-83db-4940-b48e-e5e4435b1cc3.jpg,https://cf.cjdropshipping.com/ff263fba-f937-4ebd-84c4-e41668574edf.jpg</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Step into summer with the Hot New Summer Women's Elegant Maxi Tiered Dress! This stunning piece features a flowy silhouette, delicate layers, and vibrant colors that exude sophistication. Perfect for beach outings or garden parties, it combines comfort and style effortlessly. Make a statement and turn heads this season!</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>7</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJLY291266501AZ'], ['White-M', 'CJLY291266502BY'], ['White-L', 'CJLY291266503CX'], ['White-XL', 'CJLY291266504DW'], ['White-XXL', 'CJLY291266505EV'], ['Pink-S', 'CJLY291266506FU'], ['Pink-M', 'CJLY291266507GT'], ['Pink-L', 'CJLY291266508HS'], ['Pink-XL', 'CJLY291266509IR'], ['Pink-XXL', 'CJLY291266510JQ'], ['Yellow-S', 'CJLY291266511KP'], ['Yellow-M', 'CJLY291266512LO'], ['Yellow-L', 'CJLY291266513MN'], ['Yellow-XL', 'CJLY291266514NM'], ['Yellow-XXL', 'CJLY291266515OL'], ['Green-S', 'CJLY291266516PK'], ['Green-M', 'CJLY291266517QJ'], ['Green-L', 'CJLY291266518RI'], ['Green-XL', 'CJLY291266519SH'], ['Green-XXL', 'CJLY291266520TG'], ['Light Blue-S', 'CJLY291266521UF'], ['Light Blue-M', 'CJLY291266522VE'], ['Light Blue-L', 'CJLY291266523WD'], ['Light Blue-XL', 'CJLY291266524XC'], ['Light Blue-XXL', 'CJLY291266525YB'], ['Beige-S', 'CJLY291266526ZA'], ['Beige-M', 'CJLY291266527AZ'], ['Beige-L', 'CJLY291266528BY'], ['Beige-XL', 'CJLY291266529CX'], ['Beige-XXL', 'CJLY291266530DW'], ['Purple-S', 'CJLY291266531EV'], ['Purple-M', 'CJLY291266532FU'], ['Purple-L', 'CJLY291266533GT'], ['Purple-XL', 'CJLY291266534HS'], ['Purple-XXL', 'CJLY291266535IR'], ['Navy Blue-S', 'CJLY291266536JQ'], ['Navy Blue-M', 'CJLY291266537KP'], ['Navy Blue-L', 'CJLY291266538LO'], ['Navy Blue-XL', 'CJLY291266539MN'], ['Navy Blue-XXL', 'CJLY291266540NM'], ['Red-S', 'CJLY291266541OL'], ['Red-M', 'CJLY291266542PK'], ['Red-L', 'CJLY291266543QJ'], ['Red-XL', 'CJLY291266544RI'], ['Red-XXL', 'CJLY291266545SH']]</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>300</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>CJLY2912665</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>2059830000415182849</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>lt1nxhuhwqemzjmbcvvmje9a</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>New Hot Sale Women's 2-Piece Set, Fashion Elegant Loose V-Neck Solid Color Casual Outfit</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/066184a4-53c6-42db-a54e-dd6ed3167da2.jpg,https://cf.cjdropshipping.com/b079c470-7e1f-4c85-ad59-bdb4bccff5d0.jpg,https://cf.cjdropshipping.com/f6de9133-038c-47bf-91b5-e0f7cdb95497.jpg,https://cf.cjdropshipping.com/062817c5-2f66-42b5-a070-30963bbcd92e.jpg,https://cf.cjdropshipping.com/344dbbe7-678e-4242-a530-efe4e20ac6a3.jpg,https://cf.cjdropshipping.com/6369733d-c9fe-4e79-8166-8171145cdacd.jpg</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Discover the ultimate blend of style and comfort with our New Hot Sale Women's 2-Piece Set. This elegant, loose-fitting V-Neck outfit showcases a chic solid color design that's perfect for casual outings. Enjoy effortless fashion while staying relaxed and confident. Transform your wardrobe with this stylish ensemble today!</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>9</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJTZ291102501AZ'], ['White-M', 'CJTZ291102502BY'], ['White-L', 'CJTZ291102503CX'], ['White-XL', 'CJTZ291102504DW'], ['White-XXL', 'CJTZ291102505EV'], ['White-3XL', 'CJTZ291102506FU'], ['Neon Green-S', 'CJTZ291102507GT'], ['Neon Green-M', 'CJTZ291102508HS'], ['Neon Green-L', 'CJTZ291102509IR'], ['Neon Green-XL', 'CJTZ291102510JQ'], ['Neon Green-XXL', 'CJTZ291102511KP'], ['Neon Green-3XL', 'CJTZ291102512LO'], ['Sky Blue-S', 'CJTZ291102513MN'], ['Sky Blue-M', 'CJTZ291102514NM'], ['Sky Blue-L', 'CJTZ291102515OL'], ['Sky Blue-XL', 'CJTZ291102516PK'], ['Sky Blue-XXL', 'CJTZ291102517QJ'], ['Sky Blue-3XL', 'CJTZ291102518RI'], ['Dark Purple-S', 'CJTZ291102519SH'], ['Dark Purple-M', 'CJTZ291102520TG'], ['Dark Purple-L', 'CJTZ291102521UF'], ['Dark Purple-XL', 'CJTZ291102522VE'], ['Dark Purple-XXL', 'CJTZ291102523WD'], ['Dark Purple-3XL', 'CJTZ291102524XC'], ['Khaki-S', 'CJTZ291102525YB'], ['Khaki-M', 'CJTZ291102526ZA'], ['Khaki-L', 'CJTZ291102527AZ'], ['Khaki-XL', 'CJTZ291102528BY'], ['Khaki-XXL', 'CJTZ291102529CX'], ['Khaki-3XL', 'CJTZ291102530DW'], ['Black-S', 'CJTZ291102531EV'], ['Black-M', 'CJTZ291102532FU'], ['Black-L', 'CJTZ291102533GT'], ['Black-XL', 'CJTZ291102534HS'], ['Black-XXL', 'CJTZ291102535IR'], ['Black-3XL', 'CJTZ291102536JQ']]</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>320</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>CJTZ2911025</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>2059624022247772161</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>zo76tdqznay1tzrknerm1188</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026 Spring European American Women Strapless Smocked Bodice Jumpsuit, TieDetail Casual Playsuit</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/24c46ef5-ccd0-43f0-90d6-bfab4a9fbc92.jpg,https://cf.cjdropshipping.com/31a20078-379f-46a0-a145-b222c7cb9a40.jpg,https://cf.cjdropshipping.com/b8d84a3f-986f-404e-aebf-bc04230bcdf2.jpg,https://cf.cjdropshipping.com/30d0ca3e-1f79-4e16-ab8f-e77869f1b56c.jpg,https://cf.cjdropshipping.com/7848b380-54e7-4c13-b5fe-bf596de78703.jpg,https://cf.cjdropshipping.com/bc29358b-2142-4f6b-a5ec-63bdeb6a112c.jpg</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>69</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Step into elegance this spring with our 2026 Spring European American Women Strapless Smocked Bodice Jumpsuit. This stylish tie-detail playsuit offers a perfect blend of comfort and chic. Ideal for casual outings or special occasions, it effortlessly complements your wardrobe, ensuring you look stunning and feel fabulous all day long!</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Rompers</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>30</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJLT290468401AZ'], ['Black-M', 'CJLT290468402BY'], ['Black-L', 'CJLT290468403CX'], ['Black-XL', 'CJLT290468404DW'], ['Black-XXL', 'CJLT290468405EV'], ['Pink-S', 'CJLT290468406FU'], ['Pink-M', 'CJLT290468407GT'], ['Pink-L', 'CJLT290468408HS'], ['Pink-XL', 'CJLT290468409IR'], ['Pink-XXL', 'CJLT290468410JQ'], ['Burgundy-S', 'CJLT290468416PK'], ['Burgundy-M', 'CJLT290468417QJ'], ['Burgundy-L', 'CJLT290468418RI'], ['Burgundy-XL', 'CJLT290468419SH'], ['Burgundy-XXL', 'CJLT290468420TG'], ['Green-S', 'CJLT290468421UF'], ['Green-M', 'CJLT290468422VE'], ['Green-L', 'CJLT290468423WD'], ['Green-XL', 'CJLT290468424XC'], ['Green-XXL', 'CJLT290468425YB'], ['White-S', 'CJLT290468426ZA'], ['White-M', 'CJLT290468427AZ'], ['White-L', 'CJLT290468428BY'], ['White-XL', 'CJLT290468429CX'], ['White-XXL', 'CJLT290468430DW']]</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>280</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>CJLT2904684</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>2059208970025095169</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>dumwamfwe3jbsdlll7dxgg27</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Seamless No Ride-Up Underwear - 360 Breathable &amp; Double-Layer Crotch Panties</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/cb7d398a-4c65-4c9a-abab-1a1df1129e51.jpg,https://cf.cjdropshipping.com/ce89d20c-c51e-42d4-a3a1-dc6fd5baae50.png,https://cf.cjdropshipping.com/91a856fc-da28-48fc-ad04-b325fb6785ee.png,https://cf.cjdropshipping.com/678a8875-92e3-4c36-8eac-4ba3b8b30c43.jpg,https://cf.cjdropshipping.com/41205bd9-75a4-49d4-b196-4a1862fb09d3.png,https://cf.cjdropshipping.com/ed8500d0-f9f0-4794-9163-9bdc4c88b939.png</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Experience ultimate comfort with our Seamless No Ride-Up Underwear. Designed with 360-degree breathability and a double-layer crotch, these panties offer a perfect fit without irritation. Enjoy all-day confidence and freedom of movement, making them an essential addition to your wardrobe. Embrace style and comfort like never before!</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Underwears , Panties</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>7</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJNK290392601AZ'], ['Black-M', 'CJNK290392602BY'], ['Black-L', 'CJNK290392603CX'], ['Black-XL', 'CJNK290392604DW'], ['Black-2XL', 'CJNK290392605EV'], ['Black-3XL', 'CJNK290392606FU'], ['Black-4XL', 'CJNK290392607GT'], ['Black-5XL', 'CJNK290392608HS'], ['Skin-S', 'CJNK290392609IR'], ['Skin-M', 'CJNK290392610JQ'], ['Skin-L', 'CJNK290392611KP'], ['Skin-XL', 'CJNK290392612LO'], ['Skin-2XL', 'CJNK290392613MN'], ['Skin-3XL', 'CJNK290392614NM'], ['Skin-4XL', 'CJNK290392615OL'], ['Skin-5XL', 'CJNK290392616PK'], ['Red-S', 'CJNK290392617QJ'], ['Red-M', 'CJNK290392618RI'], ['Red-L', 'CJNK290392619SH'], ['Red-XL', 'CJNK290392620TG'], ['Red-2XL', 'CJNK290392621UF'], ['Red-3XL', 'CJNK290392622VE'], ['Red-4XL', 'CJNK290392623WD'], ['Red-5XL', 'CJNK290392624XC']]</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>75</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>CJNK2903926</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>2059121318110220289</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>h5u45z5y7rk07npjkrhibah7</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Loose Fit Linen Blend Shirt &amp; Wide Leg Pants Two-Piece Set</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/bdbffb99-3d89-48bd-a79e-aedb0b96be83.jpg,https://cf.cjdropshipping.com/f4a6b4d5-ac25-4361-9001-bb28875cffe6.jpg,https://cf.cjdropshipping.com/ab3642f7-fd1e-4d4e-9a74-ef150527de05.jpg,https://cf.cjdropshipping.com/0e15696d-bfd0-45a9-9088-52c7f4896244.jpg</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Loose Fit Linen Blend Shirt &amp; Wide Leg Pants Two-Piece Set offers an effortlessly chic ensemble perfect for any occasion. Crafted from breathable materials, this stylish combo combines comfort and fashion seamlessly. Embrace laid-back elegance and stay cool while turning heads. A versatile wardrobe essential that's sure to enhance your collection!</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>13</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJTZ290419301AZ'], ['White-M', 'CJTZ290419302BY'], ['White-L', 'CJTZ290419303CX'], ['White-XL', 'CJTZ290419304DW'], ['White-2XL', 'CJTZ290419305EV'], ['White-3XL', 'CJTZ290419306FU'], ['White-4XL', 'CJTZ290419307GT'], ['White-5XL', 'CJTZ290419308HS'], ['Burgundy-S', 'CJTZ290419309IR'], ['Burgundy-M', 'CJTZ290419310JQ'], ['Burgundy-L', 'CJTZ290419311KP'], ['Burgundy-XL', 'CJTZ290419312LO'], ['Burgundy-2XL', 'CJTZ290419313MN'], ['Burgundy-3XL', 'CJTZ290419314NM'], ['Burgundy-4XL', 'CJTZ290419315OL'], ['Burgundy-5XL', 'CJTZ290419316PK'], ['Blue-S', 'CJTZ290419317QJ'], ['Blue-M', 'CJTZ290419318RI'], ['Blue-L', 'CJTZ290419319SH'], ['Blue-XL', 'CJTZ290419320TG'], ['Blue-2XL', 'CJTZ290419321UF'], ['Blue-3XL', 'CJTZ290419322VE'], ['Blue-4XL', 'CJTZ290419323WD'], ['Blue-5XL', 'CJTZ290419324XC'], ['Khaki-S', 'CJTZ290419325YB'], ['Khaki-M', 'CJTZ290419326ZA'], ['Khaki-L', 'CJTZ290419327AZ'], ['Khaki-XL', 'CJTZ290419328BY'], ['Khaki-2XL', 'CJTZ290419329CX'], ['Khaki-3XL', 'CJTZ290419330DW'], ['Khaki-4XL', 'CJTZ290419331EV'], ['Khaki-5XL', 'CJTZ290419332FU']]</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>430</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>1</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>CJTZ2904193</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>2059150055831089154</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>i9rudaxowj7m01yj70uueu01</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Spaghetti Strap Dress Women's Summer New Solid Color Casual Loose &amp; Comfortable Long Dresses</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/7c8372a3-e070-4324-abf9-4be356474e03.jpg,https://cf.cjdropshipping.com/59a5fece-07ab-4951-a96e-89792a07d327.jpg,https://cf.cjdropshipping.com/5923904b-2045-40d4-a553-26e1b36bc2ed.jpg,https://oss-cf.cjdropshipping.com/product/2026/06/30/11/4adc3049-8d65-45e8-8a04-1fc8666412f1.jpg,https://cf.cjdropshipping.com/19161613-2d69-4cef-8c46-9e143d46a76e.jpg,https://cf.cjdropshipping.com/912ee5ac-b149-4bed-8650-59343e5674d8.jpg,https://cf.cjdropshipping.com/a9b4168c-9449-437c-9094-0d9881ee9e75.jpg</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Embrace effortless elegance this summer with our Spaghetti Strap Dress. Designed in solid colors, this casual yet stylish long dress offers a loose fit for ultimate comfort. Perfect for beach outings or casual brunches, it's your go-to choice for warm weather. Stay chic and comfortable all day with this must-have piece!</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>18</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJLY290464201AZ'], ['White-M', 'CJLY290464202BY'], ['White-L', 'CJLY290464203CX'], ['White-XL', 'CJLY290464204DW'], ['White-XXL', 'CJLY290464205EV'], ['Black-S', 'CJLY290464206FU'], ['Black-M', 'CJLY290464207GT'], ['Black-L', 'CJLY290464208HS'], ['Black-XL', 'CJLY290464209IR'], ['Black-XXL', 'CJLY290464210JQ'], ['Red-S', 'CJLY290464211KP'], ['Red-M', 'CJLY290464212LO'], ['Red-L', 'CJLY290464213MN'], ['Red-XL', 'CJLY290464214NM'], ['Red-XXL', 'CJLY290464215OL'], ['Green-S', 'CJLY290464221UF'], ['Green-M', 'CJLY290464222VE'], ['Green-L', 'CJLY290464223WD'], ['Green-XL', 'CJLY290464224XC'], ['Green-XXL', 'CJLY290464225YB'], ['Blue-S', 'CJLY290464226ZA'], ['Blue-M', 'CJLY290464227AZ'], ['Blue-L', 'CJLY290464228BY'], ['Blue-XL', 'CJLY290464229CX'], ['Blue-XXL', 'CJLY290464230DW']]</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>215</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>1</v>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>CJLY2904642</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>2059203140186034177</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0typ1ke9iuzi1y3tmzo7men1</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Women's V-Neck Sleeveless  Tank Dress, Casual Summer Vacation Outfit</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/04021908-b01f-4fcb-84b6-797380ea4c7e.png,https://cf.cjdropshipping.com/892a4ca8-e3c7-4b09-bf8d-6de0967bc14e.png,https://cf.cjdropshipping.com/8a6f69f2-a2a3-4571-852c-df0059cebdf6.png,https://cf.cjdropshipping.com/c125c54f-16d8-46b4-a47c-a25a8937de12.png,https://cf.cjdropshipping.com/9b4b2cc6-cddb-4406-bea3-e5ebfaf395f1.png,https://cf.cjdropshipping.com/62076ba7-7043-4979-a62b-f973a67cd676.png,https://cf.cjdropshipping.com/12ed8831-53e9-4a26-8cbb-d0fc7e6628f2.png</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Introducing the Women's V-Neck Sleeveless Tank Dress, your go-to casual outfit for summer vacations! Crafted for comfort and style, this dress features a flattering silhouette perfect for sunny days. Pair it with sandals for a relaxed look or dress it up for evening outings. Embrace effortless elegance all season long!</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>3</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJLY290457001AZ'], ['White-M', 'CJLY290457002BY'], ['White-L', 'CJLY290457003CX'], ['White-XL', 'CJLY290457004DW'], ['White-XXL', 'CJLY290457005EV'], ['Black-S', 'CJLY290457006FU'], ['Black-M', 'CJLY290457007GT'], ['Black-L', 'CJLY290457008HS'], ['Black-XL', 'CJLY290457009IR'], ['Black-XXL', 'CJLY290457010JQ'], ['Navy-S', 'CJLY290457011KP'], ['Navy-M', 'CJLY290457012LO'], ['Navy-L', 'CJLY290457013MN'], ['Navy-XL', 'CJLY290457014NM'], ['Navy-XXL', 'CJLY290457015OL'], ['Yellow-S', 'CJLY290457016PK'], ['Yellow-M', 'CJLY290457017QJ'], ['Yellow-L', 'CJLY290457018RI'], ['Yellow-XL', 'CJLY290457019SH'], ['Yellow-XXL', 'CJLY290457020TG'], ['Burgundy-S', 'CJLY290457021UF'], ['Burgundy-M', 'CJLY290457022VE'], ['Burgundy-L', 'CJLY290457023WD'], ['Burgundy-XL', 'CJLY290457024XC'], ['Burgundy-XXL', 'CJLY290457025YB'], ['Sky Blue-S', 'CJLY290457026ZA'], ['Sky Blue-M', 'CJLY290457027AZ'], ['Sky Blue-L', 'CJLY290457028BY'], ['Sky Blue-XL', 'CJLY290457029CX'], ['Sky Blue-XXL', 'CJLY290457030DW'], ['Khaki-S', 'CJLY290457031EV'], ['Khaki-M', 'CJLY290457032FU'], ['Khaki-L', 'CJLY290457033GT'], ['Khaki-XL', 'CJLY290457034HS'], ['Khaki-XXL', 'CJLY290457035IR']]</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>255</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>1</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>CJLY2904570</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>2059197122200842242</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>imhj0jow9ladwuilhrtmmz6z</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Women's Oversized Shirt Dress, Contrast Trim Rolled Sleeve Button Down Maxi Dress For Spring Summer</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/2832a86e-f932-4c29-9926-cda7c40581a9.jpg,https://cf.cjdropshipping.com/85c2401f-0dc5-4da6-853e-9551cab84131.jpg,https://cf.cjdropshipping.com/8554855e-be1b-4a29-87da-2231d6d37e83.jpg,https://cf.cjdropshipping.com/09f8140f-7977-4fd2-8fa7-fed2ef87e7a6.jpg,https://cf.cjdropshipping.com/407ffd44-7c66-4008-9ddc-36031657f7c2.jpg</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Unleash your style this spring and summer with our Women's Oversized Shirt Dress. Featuring contrast trim and rolled sleeves, this button-down maxi dress combines comfort and chic effortlessly. Its relaxed fit is perfect for warm days, making it a must-have addition to your wardrobe. Step out in confidence and flair!</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>6</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>[['Pink-S', 'CJLY290282301AZ'], ['Pink-M', 'CJLY290282302BY'], ['Pink-L', 'CJLY290282303CX'], ['Pink-XL', 'CJLY290282304DW'], ['Pink-XXL', 'CJLY290282305EV'], ['Black-S', 'CJLY290282306FU'], ['Black-M', 'CJLY290282307GT'], ['Black-L', 'CJLY290282308HS'], ['Black-XL', 'CJLY290282309IR'], ['Black-XXL', 'CJLY290282310JQ'], ['Blue-S', 'CJLY290282316PK'], ['Blue-M', 'CJLY290282317QJ'], ['Blue-L', 'CJLY290282318RI'], ['Blue-XL', 'CJLY290282319SH'], ['Blue-XXL', 'CJLY290282320TG'], ['Green-S', 'CJLY290282321UF'], ['Green-M', 'CJLY290282322VE'], ['Green-L', 'CJLY290282323WD'], ['Green-XL', 'CJLY290282324XC'], ['Green-XXL', 'CJLY290282325YB']]</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>364</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>CJLY2902823</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>2058812335566540801</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>qdya099ipmtc6a504wms4h2l</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2024 Cross-Border European And American Amazon.com Autumn And Winter New Style Comfortable Leisure Hooded Loose Round Neck Fashion Long-Sleeve Hoodie For Women</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/13b04322-1637-4a34-83db-04b240d805fe.jpg,https://cf.cjdropshipping.com/4f22e549-f5e0-4185-9f04-e0606d364cb5.jpg</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>51</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Step into comfort and style with our 2024 Autumn and Winter hoodie for women. Featuring a relaxed fit and chic round neck design, this long-sleeve piece combines practicality and fashion effortlessly. Perfect for casual outings or cozy nights, it’s a must-have addition to your seasonal wardrobe. Embrace your unique flair!</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Woman Hoodies , Sweatshirts</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>12</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>[['Blue-S', 'CJWY290357101AZ'], ['Blue-M', 'CJWY290357102BY'], ['Blue-L', 'CJWY290357103CX'], ['Blue-XL', 'CJWY290357104DW'], ['Blue-2XL', 'CJWY290357105EV']]</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>300</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>1</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>CJWY2903571</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>2058941370373287937</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>e4owqe3fbbxvu97tnhnx354u</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Bow Tie Lace Trim Waist Cinched Peplum Cami Top</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/4a304431-390e-4a18-b932-611c3d5c3240.png,https://cf.cjdropshipping.com/e83871c2-8731-4aa2-ae68-c0256bb17847.png</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Discover the charming Bow Tie Lace Trim Waist Cinched Peplum Cami Top. Delicate lace accents highlight your silhouette, while the playful bow tie adds a touch of whimsy. Perfect for any occasion, this versatile top pairs effortlessly with your favorite jeans or skirts, ensuring you feel stylish and confident wherever you go!</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Women's Camis</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>[['Yellow-S', 'CJWC290096201AZ'], ['Yellow-M', 'CJWC290096202BY'], ['Yellow-L', 'CJWC290096203CX'], ['Yellow-XL', 'CJWC290096204DW'], ['Yellow-2XL', 'CJWC290096205EV']]</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>144</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>1</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>CJWC2900962</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>2058008097091317761</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>inwzl68gsr2bfg451g0dz4ml</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Butterfly Print Halter V-Neck Asymmetric Hem Top</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/b7ba7744-a2f8-41fd-b467-92830cd3bebe.png,https://cf.cjdropshipping.com/af95eb22-6e9a-4456-be6d-2b72f01fc37c.png</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Unleash your style with our Butterfly Print Halter V-Neck Asymmetric Hem Top. This stunning piece features a vibrant butterfly design, exuding playful elegance. The flattering halter neckline and unique hem create a chic silhouette perfect for any occasion. Make a statement and embrace your individuality with this must-have wardrobe addition.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Women's Camis</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>[['Olive Green-S', 'CJWC290114301AZ'], ['Olive Green-M', 'CJWC290114302BY'], ['Olive Green-L', 'CJWC290114303CX'], ['Olive Green-XL', 'CJWC290114304DW'], ['Olive Green-2XL', 'CJWC290114305EV']]</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>90</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>CJWC2901143</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>2058033246012272642</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cwx8f1fl6c3a7btypetbboqa</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Sleeveless Waisted Wide-Leg Jumpsuit</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/b352f42c-66a9-4317-ac71-72bb288e2785.png,https://cf.cjdropshipping.com/83fee6a7-093f-4151-ba75-af347f8171f9.png</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Introducing the Sleeveless Waisted Wide-Leg Jumpsuit—your perfect blend of comfort and sophistication. This chic piece features a flattering silhouette that adapts to any occasion. Its breathable fabric and stylish design make it an essential addition to your wardrobe. Effortlessly transition from day to night, turning heads wherever you go!</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Jumpsuits</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>[['White  Blue-S', 'CJLS290103501AZ'], ['White  Blue-M', 'CJLS290103502BY'], ['White  Blue-L', 'CJLS290103503CX'], ['White  Blue-XL', 'CJLS290103504DW'], ['White  Blue-2XL', 'CJLS290103505EV']]</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>377</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>1</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>CJLS2901035</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>2058018598210428929</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>0ir7ztzomdf1pw1hd5ay3fem</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Stylish Loose V-neck Long Striped Sleeve Shirt Dress For Women Summer</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/dbf2e1ee-dd23-40da-bd79-7d745c75f202.jpg,https://cf.cjdropshipping.com/1a392b9d-c651-415f-90a7-c54188fbcfea.jpg,https://cf.cjdropshipping.com/598da871-3d8d-4b29-9917-3ba7659ffeae.jpg,https://cf.cjdropshipping.com/19d2d82e-4bb9-44dd-8421-d51135a62ff1.jpg,https://cf.cjdropshipping.com/238b8ed2-2d96-4af4-b226-863606b8bab2.jpg,https://cf.cjdropshipping.com/b2301894-3799-486d-bac9-d8938d5b61f7.jpg</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Embrace summer elegance with our Stylish Loose V-neck Long Striped Sleeve Shirt Dress. This chic piece effortlessly combines comfort and flair, featuring a relaxed fit and trendy stripes. Perfect for casual outings or beach days, its versatile design pairs beautifully with sandals or sneakers. Elevate your wardrobe with this must-have dress!</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>9</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJLY289976101AZ'], ['Black-M', 'CJLY289976102BY'], ['Black-L', 'CJLY289976103CX'], ['Black-XL', 'CJLY289976104DW'], ['Black-XXL', 'CJLY289976105EV'], ['Black-3XL', 'CJLY289976106FU'], ['Green-S', 'CJLY289976107GT'], ['Green-M', 'CJLY289976108HS'], ['Green-L', 'CJLY289976109IR'], ['Green-XL', 'CJLY289976110JQ'], ['Green-XXL', 'CJLY289976111KP'], ['Green-3XL', 'CJLY289976112LO'], ['Red-S', 'CJLY289976113MN'], ['Red-M', 'CJLY289976114NM'], ['Red-L', 'CJLY289976115OL'], ['Red-XL', 'CJLY289976116PK'], ['Red-XXL', 'CJLY289976117QJ'], ['Red-3XL', 'CJLY289976118RI'], ['Dark brown-S', 'CJLY289976119SH'], ['Dark brown-M', 'CJLY289976120TG'], ['Dark brown-L', 'CJLY289976121UF'], ['Dark brown-XL', 'CJLY289976122VE'], ['Dark brown-XXL', 'CJLY289976123WD'], ['Dark brown-3XL', 'CJLY289976124XC'], ['Pink-S', 'CJLY289976125YB'], ['Pink-M', 'CJLY289976126ZA'], ['Pink-L', 'CJLY289976127AZ'], ['Pink-XL', 'CJLY289976128BY'], ['Pink-XXL', 'CJLY289976129CX'], ['Pink-3XL', 'CJLY289976130DW'], ['Blue-S', 'CJLY289976131EV'], ['Blue-M', 'CJLY289976132FU'], ['Blue-L', 'CJLY289976133GT'], ['Blue-XL', 'CJLY289976134HS'], ['Blue-XXL', 'CJLY289976135IR'], ['Blue-3XL', 'CJLY289976136JQ']]</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>367</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>CJLY2899761</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>2057655149431803906</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>g2a4mz115jby34rhsqemc7pt</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>V-Neck Embroidered Linen Cotton Blend Short Sleeve Blouse</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/f8f9688d-708e-4098-a7b3-8d2ea335942a.jpg,https://cf.cjdropshipping.com/b89a31e7-9190-46d1-8c3c-34654f6c09c9.jpg,https://cf.cjdropshipping.com/ae0a38d9-de0b-4294-9b38-c651255e2dea.jpg,https://cf.cjdropshipping.com/cd35c6e1-1e27-42e4-a958-1d2a590b1cd0.jpg,https://cf.cjdropshipping.com/0b69b6e2-950d-435f-b148-28a487f49f4d.jpg</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Discover effortless style with our V-Neck Embroidered Linen Cotton Blend Short Sleeve Blouse. This chic piece combines comfort and elegance, featuring delicate embroidery that enhances your look. Perfect for casual outings or dressed-up occasions, it’s versatile and breathable. Update your wardrobe with this must-have blouse today and stand out beautifully!</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Blouses , Shirts</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>[['White-M', 'CJCS289982601AZ'], ['White-L', 'CJCS289982602BY'], ['White-XL', 'CJCS289982603CX'], ['White-2XL', 'CJCS289982604DW'], ['Black-M', 'CJCS289982605EV'], ['Black-L', 'CJCS289982606FU'], ['Black-XL', 'CJCS289982607GT'], ['Black-2XL', 'CJCS289982608HS'], ['Pink-M', 'CJCS289982609IR'], ['Pink-L', 'CJCS289982610JQ'], ['Pink-XL', 'CJCS289982611KP'], ['Pink-2XL', 'CJCS289982612LO'], ['Navy Blue-M', 'CJCS289982613MN'], ['Navy Blue-L', 'CJCS289982614NM'], ['Navy Blue-XL', 'CJCS289982615OL'], ['Navy Blue-2XL', 'CJCS289982616PK'], ['Light Blue-M', 'CJCS289982617QJ'], ['Light Blue-L', 'CJCS289982618RI'], ['Light Blue-XL', 'CJCS289982619SH'], ['Light Blue-2XL', 'CJCS289982620TG']]</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>250</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>CJCS2899826</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>2057659146951643137</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>l3htrxikc0o6rotzrtvthrt9</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>White Cotton-Linen Short-Sleeve Shirt With Dragonfly Embroidery</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/ab371a63-ba7d-4eeb-a28c-cfc716317eda.png,https://cf.cjdropshipping.com/6bc2a552-3119-4a59-a710-b1b1bb9fe674.png</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Discover our White Cotton-Linen Short-Sleeve Shirt adorned with exquisite dragonfly embroidery. This stylish and breathable piece combines comfort with elegance, perfect for sunny days or relaxed evenings. Its unique design adds a touch of nature-inspired charm to any wardrobe, making it an essential addition for those who appreciate both fashion and artful details.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Blouses , Shirts</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>2</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJCS289921001AZ'], ['White-M', 'CJCS289921002BY'], ['White-L', 'CJCS289921003CX'], ['White-XL', 'CJCS289921004DW'], ['White-2XL', 'CJCS289921005EV']]</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>205</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>1</v>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>CJCS2899210</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>2057383874817466370</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>7mxxf681df9rhchbd2j6dqcp</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Summer-style Textured Sleeveless Top And Striped Shorts Set</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/bcdecb7f-ca6e-4c85-aa8c-fede7b3a15db.jpg,https://cf.cjdropshipping.com/374eb75d-a35c-44c4-995d-0a38fbcddc40.jpg</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>60</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Embrace summer vibes with our Textured Sleeveless Top and Striped Shorts Set. This stylish ensemble features a breathable fabric, perfect for warm days. The playful stripes add a trendy flair, while the relaxed fit ensures comfort and ease. Ideal for beach outings or casual gatherings, this set is a must-have!</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>[['Orange-S', 'CJTZ289878901AZ'], ['Orange-M', 'CJTZ289878902BY'], ['Orange-L', 'CJTZ289878903CX'], ['Orange-XL', 'CJTZ289878904DW'], ['Orange-XXL', 'CJTZ289878905EV']]</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>300</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>1</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>CJTZ2898789</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>2057338709738299394</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>x8lldoxdh2t39c2l32nhhu69</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Bohemian Style Textured Pleated Deep V White Top</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/14d527a4-92c7-44b2-ab48-94863f75fb83.jpg,https://cf.cjdropshipping.com/4df786fc-1292-4654-9731-1d2e1891a2af.jpg</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Add a touch of bohemian flair to your wardrobe with our Textured Pleated Deep V White Top. This stylish piece features intricate detailing and a flattering silhouette, perfect for any occasion. Its lightweight fabric ensures all-day comfort while keeping you chic. Embrace effortless elegance and update your collection today!</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Women's Long-Sleeved Shirts</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJWL289877701AZ'], ['White-M', 'CJWL289877702BY'], ['White-L', 'CJWL289877703CX'], ['White-XL', 'CJWL289877704DW'], ['White-XXL', 'CJWL289877705EV']]</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>150</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>1</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>CJWL2898777</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>2057337147464916994</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ov0b7kk8z44siyd8yhdlu3f7</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>White &amp; Black Contrast High-Neck Short-Sleeve Top &amp; Pleated Skirt Set</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/bd8e1c02-dbcf-44b0-858f-b4cb21fabb67.png,https://cf.cjdropshipping.com/6eb36c22-cc02-4283-bb7e-54cf6660f4e1.png</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>60</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Showcase your style with the stunning White &amp; Black Contrast High-Neck Short-Sleeve Top &amp; Pleated Skirt Set. This chic ensemble effortlessly combines elegance and comfort, making it perfect for any occasion. Enjoy the flattering silhouette and modern design that will turn heads and ensure you stand out wherever you go.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJTZ289860601AZ'], ['White-M', 'CJTZ289860602BY'], ['White-L', 'CJTZ289860603CX'], ['White-XL', 'CJTZ289860604DW'], ['White-2XL', 'CJTZ289860605EV']]</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>285</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>CJTZ2898606</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>2057303014739058689</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ar0x44jybbcbrci1g8uja0pf</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Y2K Leopard Print Halter Ruching Bodycon Dress</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/f72faabe-24f5-468d-977b-ba305c89d2a3.png,https://cf.cjdropshipping.com/ae23c7ce-8bc5-405d-be77-9a4d66389101.png</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>60</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Unleash your wild side with our Y2K Leopard Print Halter Ruching Bodycon Dress. This stunning piece hugs your curves in all the right places while showcasing a fierce, playful pattern. Perfect for nights out or spontaneous adventures, it combines bold style with ultimate comfort. Stand out and make a statement effortlessly!</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>[['Brown-S', 'CJLY289905901AZ'], ['Brown-M', 'CJLY289905902BY'], ['Brown-L', 'CJLY289905903CX'], ['Brown-XL', 'CJLY289905904DW'], ['Brown-2XL', 'CJLY289905905EV']]</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>194</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>CJLY2899059</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>2057367961670033409</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>eqybyg0to3jkzoqrs9pu1e37</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>White Cotton-Linen Camisole With Dragonfly Embroidery</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/5bfa0db0-9681-4247-81b6-025dda0ed8e6.png,https://cf.cjdropshipping.com/39ba8c3c-379f-4bd6-a77d-7c553866cdf7.png</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Discover the perfect blend of comfort and elegance with our White Cotton-Linen Camisole featuring intricate dragonfly embroidery. This stylish piece is lightweight, breathable, and perfect for layering or wearing alone. Embrace the beauty of nature and enhance your wardrobe with this unique, artisan-crafted camisole that exudes charm and sophistication.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Women's Camis</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJWC289918301AZ'], ['White-M', 'CJWC289918302BY'], ['White-L', 'CJWC289918303CX'], ['White-XL', 'CJWC289918304DW'], ['White-2XL', 'CJWC289918305EV']]</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>224</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>CJWC2899183</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>2057381961941516290</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>9er3ngjkq9i6rgtuceharmr1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Vintage Cotton-Linen Floral Embroidery Boho Skirt</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/467b5fcc-3a0f-4a3f-bd65-ba6f7b871986.png,https://cf.cjdropshipping.com/318f8571-06e2-4968-a237-f76f8bb8019d.png</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Discover the charm of our Vintage Cotton-Linen Floral Embroidery Boho Skirt. Crafted for comfort and style, this skirt features intricate floral designs that embody a carefree spirit. Perfect for any occasion, its flowy silhouette adds a touch of elegance to your wardrobe. Embrace your individuality and shine bright!</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Bottoms , Skirts</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>2</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>[['Dusty Rose-S', 'CJQZ289740101AZ'], ['Dusty Rose-M', 'CJQZ289740102BY'], ['Dusty Rose-L', 'CJQZ289740103CX'], ['Dusty Rose-XL', 'CJQZ289740104DW'], ['Dusty Rose-2XL', 'CJQZ289740105EV']]</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>255</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>CJQZ2897401</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>2056996821870755842</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>rfcd1r8n95t04n8022y0du8t</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Paisley Print Loose Blouse And  Harem Pants Set</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/79cc8c69-d15e-44ec-9e0d-bc18db3a4ae3.png,https://cf.cjdropshipping.com/f1cd23f9-2d9e-477f-9579-92eed89d480d.png,https://cf.cjdropshipping.com/99e7199e-ed48-4760-9cd6-70a72973b97f.png</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Embrace effortless style with our Paisley Print Loose Blouse and Harem Pants Set. This chic ensemble combines comfort and flair, perfect for casual outings or relaxed days at home. The lightweight fabric drapes beautifully, while the vibrant paisley pattern adds a touch of bohemian elegance. Make a statement effortlessly!</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>[['Green-S', 'CJTZ289763501AZ'], ['Green-M', 'CJTZ289763502BY'], ['Green-L', 'CJTZ289763503CX'], ['Green-XL', 'CJTZ289763504DW'], ['Green-2XL', 'CJTZ289763505EV'], ['Dusty-S', 'CJTZ289763506FU'], ['Dusty-M', 'CJTZ289763507GT'], ['Dusty-L', 'CJTZ289763508HS'], ['Dusty-XL', 'CJTZ289763509IR'], ['Dusty-2XL', 'CJTZ289763510JQ'], ['Brown-S', 'CJTZ289763511KP'], ['Brown-M', 'CJTZ289763512LO'], ['Brown-L', 'CJTZ289763513MN'], ['Brown-XL', 'CJTZ289763514NM'], ['Brown-2XL', 'CJTZ289763515OL']]</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>380</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>CJTZ2897635</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>2057005535661432834</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>evrhozqloa2s5id6yhamo9nc</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Trim Wide-Leg Jumpsuit</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/05ab4446-f5c9-4723-baa4-6bbcd8655ede.png,https://cf.cjdropshipping.com/39288bec-6a94-4c3b-bad0-0b37f93f2162.png</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Trim Wide-Leg Jumpsuit
+Step into effortless elegance with our Trim Wide-Leg Jumpsuit. This chic piece features a flattering silhouette, comfortable fabric, and versatile style, perfect for any occasion. Dress it up or down for day or night, making it a must-have addition to your wardrobe. Embrace confidence in every step!</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Jumpsuits</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>4</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJLS289819701AZ'], ['Black-M', 'CJLS289819702BY'], ['Black-L', 'CJLS289819703CX'], ['Black-XL', 'CJLS289819704DW'], ['Black-2XL', 'CJLS289819705EV']]</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>374</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>CJLS2898197</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>2057044367811321857</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>pkya93w9097nky1pw9h47beo</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Bright Red Floral Print One-Shoulder High-Low Dress</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/2d463abd-8858-41f2-a741-d8ede4c85b1e.png,https://oss-cf.cjdropshipping.com/product/2026/05/20/10/92f4521c-7f96-41a8-ab2a-a15ecf4be7b5.jpg</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Step into summer with our Bright Red Floral Print One-Shoulder High-Low Dress! This stunning design showcases vibrant blooms and a trendy silhouette, making it perfect for parties or casual outings. The asymmetrical hem adds a chic touch, while the comfortable fit ensures you'll look and feel fabulous all day long!</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>[['Bright Red-S', 'CJLY289753901AZ'], ['Bright Red-M', 'CJLY289753902BY'], ['Bright Red-L', 'CJLY289753903CX'], ['Bright Red-XL', 'CJLY289753904DW'], ['Bright Red-2XL', 'CJLY289753905EV']]</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>210</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>CJLY2897539</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>2056999670767321089</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>yui5jzyhdojob2kajwi8cs2t</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Red And White Contrasted Necktie Top</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/7afa1ff2-dd8c-41ad-9b0b-40b4f8a98514.jpg,https://cf.cjdropshipping.com/02fc9384-e4a4-4002-963c-4b089012b877.jpg</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Introducing the Red and White Contrasted Necktie Top, a stylish blend of sophistication and boldness. This eye-catching design features a vibrant red base enhanced by striking white accents, perfect for making a statement. Ideal for casual outings or formal occasions, it effortlessly combines versatility and trendsetting flair. Dress to impress!</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Women's Camis</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJWC289800101AZ'], ['White-M', 'CJWC289800102BY'], ['White-L', 'CJWC289800103CX'], ['White-XL', 'CJWC289800104DW'], ['White-XXL', 'CJWC289800105EV']]</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>95</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>CJWC2898001</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>2057028582942482434</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>vfqbu06igw4fcij1sr2zr4j7</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Contrast Color Casual Neckline Wide-Leg Set</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/f14ba7d3-bd49-47df-bf10-c785755ba996.jpg,https://cf.cjdropshipping.com/4b59ea72-6545-4d21-8211-d1d0b4694e0f.jpg</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>65</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Introducing the Contrast Color Casual Neckline Wide-Leg Set! This stylish ensemble combines comfort with contemporary flair, featuring a flattering neckline and relaxed wide-leg fit. Perfect for any occasion, it exudes effortless charm. Dress it up or down for a chic look, making it an essential addition to your wardrobe today!</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJTZ289767301AZ'], ['White-M', 'CJTZ289767302BY'], ['White-L', 'CJTZ289767303CX'], ['White-XL', 'CJTZ289767304DW'], ['White-XXL', 'CJTZ289767305EV']]</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>413</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>CJTZ2897673</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>2057008566280953857</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>p11u5gckyynhuq5lzcdtpzum</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Bohemian Geometric Print Halter Cutout Romper</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/bc13e823-d43f-404f-9b35-e4817fe55205.png,https://cf.cjdropshipping.com/7dde7fcd-74e1-49f3-9803-04f397c28142.png</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Embrace effortless style with our Bohemian Geometric Print Halter Cutout Romper. This chic piece features a stunning design that combines comfort and flair. Perfect for summer outings or beach trips, its playful cutouts and flowing silhouette ensure you stand out anywhere. Slip into this versatile romper and express your unique vibe!</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Rompers</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>[['Terracotta-S', 'CJLT289720601AZ'], ['Terracotta-M', 'CJLT289720602BY'], ['Terracotta-L', 'CJLT289720603CX'], ['Terracotta-XL', 'CJLT289720604DW'], ['Terracotta-2XL', 'CJLT289720605EV']]</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>182</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>CJLT2897206</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>2056985571699343362</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>uswybs8cpkbvcdctq55if30e</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Hooded Sleeveless Half Zip Ruffle Hem Pocketed Casual Romper 2 Colors Available</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/33b06f45-6a16-4e28-b5c3-2674b40adf30.png,https://cf.cjdropshipping.com/bdf3254e-a2b9-4a2b-ba66-20eea419bbae.png</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>65</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Discover comfort and style with our Hooded Sleeveless Half Zip Ruffle Hem Pocketed Casual Romper. This versatile piece, available in two stunning colors, features a chic ruffle hem and functional pockets. Perfect for casual outings or lounging at home, this romper combines ease and fashion for a must-have addition to your wardrobe.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJTZ289629401AZ'], ['Black-M', 'CJTZ289629402BY'], ['Black-L', 'CJTZ289629403CX'], ['Black-XL', 'CJTZ289629404DW'], ['Black-XXL', 'CJTZ289629405EV'], ['Red-S', 'CJTZ289629406FU'], ['Red-M', 'CJTZ289629407GT'], ['Red-L', 'CJTZ289629408HS'], ['Red-XL', 'CJTZ289629409IR'], ['Red-XXL', 'CJTZ289629410JQ']]</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>270</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>CJTZ2896294</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>2056645503883055106</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1mc0g75lty3n4rc40um2i7cr</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Sleeveless Square Neck Corset Mermaid Maxi Dress</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/3e4a5a75-60ed-45cc-af80-0d12b1cd511f.jpg,https://cf.cjdropshipping.com/ef9ec2d0-6432-4999-a552-a0f00ab4c9e7.jpg,https://cf.cjdropshipping.com/616080c0-f903-4635-a9f9-7080d027ee1d.jpg,https://cf.cjdropshipping.com/951e363f-a833-47d0-b801-b8cd50f57e14.jpg</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>194</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Transform your wardrobe with the Sleeveless Square Neck Corset Mermaid Maxi Dress. This stunning piece features a chic square neckline and a figure-hugging corset bodice, flowing into an elegant mermaid silhouette. Perfect for special occasions or date nights, it offers both style and comfort for the confident woman. Embrace timeless beauty!</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>9</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>[['Light Pink-S', 'CJLY289587101AZ'], ['Light Pink-M', 'CJLY289587102BY'], ['Light Pink-L', 'CJLY289587103CX'], ['Light Pink-XL', 'CJLY289587104DW'], ['Black-S', 'CJLY289587105EV'], ['Black-M', 'CJLY289587106FU'], ['Black-L', 'CJLY289587107GT'], ['Black-XL', 'CJLY289587108HS'], ['Pink-S', 'CJLY289587109IR'], ['Pink-M', 'CJLY289587110JQ'], ['Pink-L', 'CJLY289587111KP'], ['Pink-XL', 'CJLY289587112LO'], ['Light Blue-S', 'CJLY289587113MN'], ['Light Blue-M', 'CJLY289587114NM'], ['Light Blue-L', 'CJLY289587115OL'], ['Light Blue-XL', 'CJLY289587116PK']]</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>500</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>CJLY2895871</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>2056615484412178434</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>96zql9wwjck7vqosuw4yr78z</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Tropical Vacation Style Printed Cropped Camisole Top  High-waisted Wide-leg Pants Set For Women</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/47f0da75-d3ef-4b49-8618-4f3deb836c60.png,https://cf.cjdropshipping.com/ef7906a9-dfd4-458a-82cf-3df4a2930c01.png</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Unleash your wanderlust with our Tropical Vacation Style Printed Cropped Camisole Top and High-waisted Wide-leg Pants Set. This vibrant ensemble features a stunning tropical print, perfect for beach days or summer outings. Enjoy ultimate comfort and style, making it an essential addition to your wardrobe for every sunny adventure!</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>[['Orange-S', 'CJTZ28944370001'], ['Orange-M', 'CJTZ28944370002'], ['Orange-L', 'CJTZ28944370003'], ['Orange-XL', 'CJTZ28944370004'], ['Orange-XXL', 'CJTZ28944370005'], ['Green-S', 'CJTZ28944370006'], ['Green-M', 'CJTZ28944370007'], ['Green-L', 'CJTZ28944370008'], ['Green-XL', 'CJTZ28944370009'], ['Green-XXL', 'CJTZ28944370010']]</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>279</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>CJTZ2894437</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>2056245598182084610</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>4r2e3mtxhpeycawmwdfhgjo6</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>European And American Elegant Hollow-Out Set For Women</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/quick/product/c005d885-f466-4b06-9890-ad1033cec171.jpg,https://cf.cjdropshipping.com/quick/product/0d48a00c-2d0b-4d22-886b-de7958014042.jpg,https://cf.cjdropshipping.com/quick/product/93c9b067-53a8-45d2-88c5-09fb45b12cde.jpg,https://cf.cjdropshipping.com/quick/product/467cbb52-5dad-450b-a724-1b6df1a35911.jpg,https://cf.cjdropshipping.com/quick/product/79ff3087-6342-4014-9963-354965f594e8.jpg,https://cf.cjdropshipping.com/quick/product/f905e801-c4d2-4111-86b0-7c9e192b586f.jpg,https://cf.cjdropshipping.com/quick/product/b92fa16d-35be-47bf-9922-f15d30e5dc23.jpg,https://cf.cjdropshipping.com/quick/product/d3727117-f538-49a4-8b78-fd0588b00152.jpg</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Discover the European and American Elegant Hollow-Out Set for Women, a perfect blend of sophistication and style. Crafted with intricate designs, this stunning set enhances your wardrobe with its delicate details. Ideal for any occasion, it elevates your look effortlessly, ensuring you shine wherever you go. Embrace elegance today!</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Women's Clothing &gt; Tops , Sets &gt; Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>8</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>[['Light Yellow-XS', 'CJTZ28946880001'], ['Light Yellow-S', 'CJTZ28946880002'], ['Light Yellow-M', 'CJTZ28946880003'], ['Light Yellow-L', 'CJTZ28946880004'], ['Light Yellow-XL', 'CJTZ28946880005'], ['Light Yellow-2XL', 'CJTZ28946880006'], ['Green-XS', 'CJTZ28946880007'], ['Green-S', 'CJTZ28946880008'], ['Green-M', 'CJTZ28946880009'], ['Green-L', 'CJTZ28946880010'], ['Green-XL', 'CJTZ28946880011'], ['Green-2XL', 'CJTZ28946880012'], ['Sky Blue-XS', 'CJTZ28946880013'], ['Sky Blue-S', 'CJTZ28946880014'], ['Sky Blue-M', 'CJTZ28946880015'], ['Sky Blue-L', 'CJTZ28946880016'], ['Sky Blue-XL', 'CJTZ28946880017'], ['Sky Blue-2XL', 'CJTZ28946880018'], ['Lotus Root Color-XS', 'CJTZ28946880019'], ['Lotus Root Color-S', 'CJTZ28946880020'], ['Lotus Root Color-M', 'CJTZ28946880021'], ['Lotus Root Color-L', 'CJTZ28946880022'], ['Lotus Root Color-XL', 'CJTZ28946880023'], ['Lotus Root Color-2XL', 'CJTZ28946880024']]</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>250</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>CJTZ2894688</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>2056279535229091842</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>w9fs4sw86ehso2xkih9gvg8j</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Lace Paneled Loose V-Neck Short Sleeves For Women</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/49d87bb4-c0aa-4096-975b-7cb2c939abbc.jpg,https://cf.cjdropshipping.com/8e0353fc-01ff-43e2-86d3-54d3866e109d.jpg,https://cf.cjdropshipping.com/48d9749b-6ed7-4ce8-a36d-2bc90c0044c8.jpg,https://cf.cjdropshipping.com/bc4b6655-e993-4559-9425-c20d437f2eda.jpg,https://cf.cjdropshipping.com/bd94b8a1-3544-4bc2-bbf4-2e6eeb4e320d.jpg,https://cf.cjdropshipping.com/4a5233bf-7367-42c5-929d-ec166b01aecc.jpg,https://oss-cf.cjdropshipping.com/product/2025/05/02/07/a4ffed6e-689e-4492-acaf-7f1443712f29.jpg,https://cf.cjdropshipping.com/16d0b44d-211e-4571-b709-2acef7b9772f.jpg</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Experience effortless elegance with our Lace Paneled Loose V-Neck Short Sleeves for Women. This stylish top features delicate lace accents that add a touch of charm to any outfit. Perfect for casual outings or dressy occasions, its comfortable fit and versatile design make it a must-have addition to your wardrobe.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Women's Clothing &gt; Outerwear , Jackets &gt; Blazers</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>9</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJQB28946860001'], ['White-M', 'CJQB28946860002'], ['Light Blue-M', 'CJQB28946860010'], ['Light Blue-L', 'CJQB28946860011'], ['Light Blue-XL', 'CJQB28946860012'], ['Light Blue-2XL', 'CJQB28946860013'], ['Light Purple-S', 'CJQB28946860017'], ['Light Purple-M', 'CJQB28946860018'], ['Light Purple-L', 'CJQB28946860019'], ['Pink-S', 'CJQB28946860025'], ['Pink-M', 'CJQB28946860026'], ['Pink-L', 'CJQB28946860027'], ['Pink-XL', 'CJQB28946860028'], ['Pink-2XL', 'CJQB28946860029'], ['Yellow-S', 'CJQB28946860033'], ['Yellow-M', 'CJQB28946860034'], ['Yellow-L', 'CJQB28946860035'], ['Yellow-XL', 'CJQB28946860036'], ['Yellow-2XL', 'CJQB28946860037'], ['Red-S', 'CJQB28946860041'], ['Red-M', 'CJQB28946860042'], ['Red-2XL', 'CJQB28946860045'], ['Grey-2XL', 'CJQB28946860049'], ['Grey-L', 'CJQB28946860053'], ['Grey-M', 'CJQB28946860054'], ['Grey-S', 'CJQB28946860055'], ['Grey-XL', 'CJQB28946860056']]</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>200</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>CJQB2894686</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>2056279448125980673</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ikro3v0i5fecqgq7h098ras6</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>3 Color Option Off Shoulder Puff Sleeve Smocked Waist Pocketed Flowy Maxi Dress</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/233eb34a-6f45-4b53-aac8-320afcad3001.png,https://cf.cjdropshipping.com/cf18d957-1d36-49ee-94e6-2539c84cccbb.png,https://cf.cjdropshipping.com/aac8c567-fe20-4d75-9fe2-736b9eafa5ee.png</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Introducing our stunning Off Shoulder Puff Sleeve Smocked Waist Pocketed Flowy Maxi Dress. Available in three beautiful colors, this dress combines effortless elegance with comfort. The smocked waist flatters your figure, while the pockets add functionality. Perfect for any occasion, this maxi exudes charm and grace, ensuring you stand out effortlessly.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>[['Red-S', 'CJTZ289351601AZ'], ['Red-M', 'CJTZ289351602BY'], ['Red-L', 'CJTZ289351603CX'], ['Red-XL', 'CJTZ289351604DW'], ['Red-XXL', 'CJTZ289351605EV'], ['Blue-S', 'CJTZ289351606FU'], ['Blue-M', 'CJTZ289351607GT'], ['Blue-L', 'CJTZ289351608HS'], ['Blue-XL', 'CJTZ289351609IR'], ['Blue-XXL', 'CJTZ289351610JQ'], ['White-S', 'CJTZ289351611KP'], ['White-M', 'CJTZ289351612LO'], ['White-L', 'CJTZ289351613MN'], ['White-XL', 'CJTZ289351614NM'], ['White-XXL', 'CJTZ289351615OL']]</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>511</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>CJTZ2893516</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>2055571830305611778</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2udloxubcg5m237h83c13x6l</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Linen Cotton Polo Neck Loose Fit Casual Dress</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/f08667e1-a73d-4f45-a0f7-485c5d1acda7.jpg,https://cf.cjdropshipping.com/1b05aba8-5e2d-4269-b829-447bf97e571e.jpg,https://cf.cjdropshipping.com/a5a80fbc-ca24-41f8-aa25-b1f4f0fb2293.jpg</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Upgrade your wardrobe with our Linen Cotton Polo Neck Loose Fit Casual Dress. Perfect for warm days, this stylish piece combines comfort and elegance effortlessly. The breathable fabric ensures all-day freshness, while the relaxed silhouette flatters every body type. Dress it up or down for versatile looks that shine.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>6</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJLY289295501AZ'], ['Black-M', 'CJLY289295502BY'], ['Black-L', 'CJLY289295503CX'], ['Black-XL', 'CJLY289295504DW'], ['Black-2XL', 'CJLY289295505EV'], ['Black-3XL', 'CJLY289295506FU'], ['Black-4XL', 'CJLY289295507GT'], ['Black-5XL', 'CJLY289295508HS'], ['Dark Grey-S', 'CJLY289295509IR'], ['Dark Grey-M', 'CJLY289295510JQ'], ['Dark Grey-L', 'CJLY289295511KP'], ['Dark Grey-XL', 'CJLY289295512LO'], ['Dark Grey-2XL', 'CJLY289295513MN'], ['Dark Grey-3XL', 'CJLY289295514NM'], ['Dark Grey-4XL', 'CJLY289295515OL'], ['Dark Grey-5XL', 'CJLY289295516PK'], ['Army Green-S', 'CJLY289295517QJ'], ['Army Green-M', 'CJLY289295518RI'], ['Army Green-L', 'CJLY289295519SH'], ['Army Green-XL', 'CJLY289295520TG'], ['Army Green-2XL', 'CJLY289295521UF'], ['Army Green-3XL', 'CJLY289295522VE'], ['Army Green-4XL', 'CJLY289295523WD'], ['Army Green-5XL', 'CJLY289295524XC']]</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>300</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>CJLY2892955</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>2055477036675735553</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>mhhxlr5ylwyqlaw3fi0vh58m</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>New European &amp; American Style Button-Detail Sleeveless Shirt Collar Dress</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/39db41bc-6e0d-43f0-b90f-34772edb4388.jpg,https://cf.cjdropshipping.com/4c7483c1-a908-4313-b4e1-65ab00a636f9.jpg,https://cf.cjdropshipping.com/21b7867d-afc6-45b7-a5d0-4bf525682542.jpg,https://cf.cjdropshipping.com/4df432dc-8486-4b36-8022-564ad7ca8293.jpg,https://cf.cjdropshipping.com/79c0089e-4a92-4daf-9c36-a91936f93e16.jpg,https://cf.cjdropshipping.com/91f6156b-389d-42d7-9789-f032444f2621.jpg,https://cf.cjdropshipping.com/ff9fba75-f917-4241-9c5a-32b72e72e665.jpg</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Introducing the New European &amp; American Style Button-Detail Sleeveless Shirt Collar Dress! This chic dress features a sophisticated collar and stylish button accents, combining elegance and comfort. Perfect for any occasion, its versatile design allows for effortless styling. Stand out with this trendy piece that enhances your wardrobe’s allure.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>4</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>[['Black-S', 'CJLY289216811KP'], ['Black-M', 'CJLY289216812LO'], ['Black-L', 'CJLY289216813MN'], ['Black-XL', 'CJLY289216814NM'], ['Black-XXL', 'CJLY289216815OL'], ['Green-S', 'CJLY289216816PK'], ['Green-M', 'CJLY289216817QJ'], ['Green-L', 'CJLY289216818RI'], ['Green-XL', 'CJLY289216819SH'], ['Green-XXL', 'CJLY289216820TG'], ['Burgundy-S', 'CJLY289216821UF'], ['Burgundy-M', 'CJLY289216822VE'], ['Burgundy-L', 'CJLY289216823WD'], ['Burgundy-XL', 'CJLY289216824XC'], ['Burgundy-XXL', 'CJLY289216825YB'], ['White-S', 'CJLY289216826ZA'], ['White-M', 'CJLY289216827AZ'], ['White-L', 'CJLY289216828BY'], ['White-XL', 'CJLY289216829CX'], ['White-XXL', 'CJLY289216830DW'], ['Khaki-S', 'CJLY289216831EV'], ['Khaki-M', 'CJLY289216832FU'], ['Khaki-L', 'CJLY289216833GT'], ['Khaki-XL', 'CJLY289216834HS'], ['Khaki-XXL', 'CJLY289216835IR']]</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>406</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>1</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>CJLY2892168</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>2055164913499160578</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>n7asnzkc2bgpnq10mzc7y0j7</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Spring Summer Casual Backless Tie Sleeveless Long Dress</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/3d3eab19-4efd-426f-a420-9a3642edc82d.jpg,https://cf.cjdropshipping.com/404ae512-b128-4b49-9797-bca51af25368.jpg,https://cf.cjdropshipping.com/79a705be-cf5f-450b-8222-256a4ce41685.jpg,https://cf.cjdropshipping.com/f7b31f5c-b0f1-4a15-98b5-c0c28d0292ab.jpg,https://cf.cjdropshipping.com/2814dc00-09f9-4dda-a3e8-12ad8308b65b.jpg</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Embrace effortless elegance this season with our Spring Summer Casual Backless Tie Sleeveless Long Dress. Crafted for comfort and style, this chic piece features a stunning backless design and playful ties, perfect for sunny days and evening outings. Make a statement wherever you go with its flowing silhouette and vibrant colors!</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>3</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>[['Pink-S', 'CJLY289260806FU'], ['Pink-M', 'CJLY289260807GT'], ['Pink-L', 'CJLY289260808HS'], ['Pink-XL', 'CJLY289260809IR'], ['Pink-XXL', 'CJLY289260810JQ'], ['Sky blue-S', 'CJLY289260811KP'], ['Sky blue-M', 'CJLY289260812LO'], ['Sky blue-L', 'CJLY289260813MN'], ['Sky blue-XL', 'CJLY289260814NM'], ['Sky blue-XXL', 'CJLY289260815OL'], ['Burgundy-S', 'CJLY289260816PK'], ['Burgundy-M', 'CJLY289260817QJ'], ['Burgundy-L', 'CJLY289260818RI'], ['Burgundy-XL', 'CJLY289260819SH'], ['Burgundy-XXL', 'CJLY289260820TG'], ['White-S', 'CJLY289260821UF'], ['White-M', 'CJLY289260822VE'], ['White-L', 'CJLY289260823WD'], ['White-XL', 'CJLY289260824XC'], ['White-XXL', 'CJLY289260825YB']]</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>458</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>CJLY2892608</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>2055217523295150081</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ikyocrc6x4pgp9bcrpj3ngiz</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Bohemian Sleeveless Chiffon Maxi Dress</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/b18d4431-b27e-43c6-b0e3-18b99c43832a.png,https://cf.cjdropshipping.com/48280bba-3b5f-40c2-b0ac-00318f9ea3b0.png,https://cf.cjdropshipping.com/8f467b45-a7f0-40ad-8d32-5aa1687c5d45.png</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Bohemian Sleeveless Chiffon Maxi Dress  
+Step into summer elegance with our Bohemian Sleeveless Chiffon Maxi Dress. This flowing, lightweight design drapes beautifully, perfect for warm days and special occasions. The vibrant patterns and comfortable fit make it a must-have addition to your wardrobe. Embrace your free spirit and make a statement wherever you go!</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>2</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>[['Classic Black-S', 'CJLY289272301AZ'], ['Classic Black-M', 'CJLY289272302BY'], ['Classic Black-L', 'CJLY289272303CX'], ['Classic Black-XL', 'CJLY289272304DW'], ['Classic Black-XXL', 'CJLY289272305EV'], ['Dusty Lavender-S', 'CJLY289272306FU'], ['Dusty Lavender-M', 'CJLY289272307GT'], ['Dusty Lavender-L', 'CJLY289272308HS'], ['Dusty Lavender-XL', 'CJLY289272309IR'], ['Dusty Lavender-XXL', 'CJLY289272310JQ'], ['White-S', 'CJLY289272311KP'], ['White-M', 'CJLY289272312LO'], ['White-L', 'CJLY289272313MN'], ['White-XL', 'CJLY289272314NM'], ['White-XXL', 'CJLY289272315OL']]</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>448</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>CJLY2892723</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>2055238608071663618</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>b79vo1px080isxqdhig5htae</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Urban Denim Two-Piece Set</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/4757544d-4aea-4ffc-9114-99337db19b2f.png,https://cf.cjdropshipping.com/66bc00d2-c7e0-43af-b4f1-ff8f4775dfad.png,https://cf.cjdropshipping.com/ea983c57-0f09-4673-a9da-6a83fcf9926f.png</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Urban Denim Two-Piece Set is the perfect blend of style and comfort. Crafted from premium denim, this chic outfit features a trendy design that effortlessly transforms your look. Ideal for casual outings or fashion-forward events, it promises to keep you feeling confident and fabulous. Step out and showcase your unique flair!</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>2</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>[['Light Denim Blue-S', 'CJTZ288959101AZ'], ['Light Denim Blue-M', 'CJTZ288959102BY'], ['Light Denim Blue-L', 'CJTZ288959103CX'], ['Light Denim Blue-XL', 'CJTZ288959104DW'], ['Light Denim Blue-XXL', 'CJTZ288959105EV'], ['Dark Brown-S', 'CJTZ288959106FU'], ['Dark Brown-M', 'CJTZ288959107GT'], ['Dark Brown-L', 'CJTZ288959108HS'], ['Dark Brown-XL', 'CJTZ288959109IR'], ['Dark Brown-XXL', 'CJTZ288959110JQ'], ['Caramel Orange-S', 'CJTZ288959111KP'], ['Caramel Orange-M', 'CJTZ288959112LO'], ['Caramel Orange-L', 'CJTZ288959113MN'], ['Caramel Orange-XL', 'CJTZ288959114NM'], ['Caramel Orange-XXL', 'CJTZ288959115OL']]</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>334</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>1</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>CJTZ2889591</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>2054748379043504130</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>jqa9vsjepbi8d15imuy5zjhx</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026 New French Retro Style Beige Stand Up Collar Waist Cinched Short Sleeved Tweed Suit</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/dd0be640-077e-48f1-86f4-df90c666079d.png,https://cf.cjdropshipping.com/aba52eac-bbf2-411a-91e5-f895f0c2e20d.png</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Introducing the 2026 New French Retro Style Beige Stand Up Collar Waist Cinched Short Sleeved Tweed Suit. This chic ensemble captures timeless elegance, featuring a flattering silhouette and luxurious tweed fabric. Perfect for sophisticated outings or stylish office wear, it effortlessly combines comfort with a refined aesthetic, elevating your wardrobe game!</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>[['Beige-S', 'CJTZ288953801AZ'], ['Beige-M', 'CJTZ288953802BY'], ['Beige-L', 'CJTZ288953803CX'], ['Beige-Xl', 'CJTZ288953804DW'], ['Beige-2xl', 'CJTZ288953805EV'], ['Black-S', 'CJTZ288953806FU'], ['Black-M', 'CJTZ288953807GT'], ['Black-L', 'CJTZ288953808HS'], ['Black-Xl', 'CJTZ288953809IR'], ['Black-2xl', 'CJTZ288953810JQ']]</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>451</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>CJTZ2889538</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>2054743631695355906</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>quw3cmt987sr4u8qvx4q48ie</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Multicolor Horizontal Stripe Deep V Neck Cap Sleeve Waist Tie Flared Mini Dress</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://oss-cf.cjdropshipping.com/product/2026/05/16/08/cf70404a-26c3-4a24-b8c0-d24e7167c010.jpg,https://oss-cf.cjdropshipping.com/product/2026/05/16/08/d35740d3-2899-4200-87bd-4339df61da05.jpg,https://oss-cf.cjdropshipping.com/product/2026/05/16/08/1a9887cb-ef89-4855-87c0-c753338b04f2.jpg</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Unleash your style with our Multicolor Horizontal Stripe Deep V Neck Cap Sleeve Waist Tie Flared Mini Dress. This vibrant design features a flattering silhouette, perfect for any occasion. The eye-catching stripes and flared skirt create a playful yet chic look, ensuring you stand out effortlessly. Embrace comfort and confidence today!</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>[['Off White-S', 'CJTZ288735201AZ'], ['Off White-M', 'CJTZ288735202BY'], ['Off White-L', 'CJTZ288735203CX'], ['Off White-XL', 'CJTZ288735204DW'], ['Off White-XXL', 'CJTZ288735205EV']]</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>266</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>CJTZ2887352</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>2054445653496795137</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>jyyk9hnkz7n4ypyj324icaxt</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>New European And American Style High-Waist Striped Drop-Seat Wide Leg Pants For Women Loose Straight Office Casual Pants</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/ab3cf9de-f900-43cb-94c6-9fb39fbc5d48.jpg,https://cf.cjdropshipping.com/a8b7efd1-a280-41d8-8f33-d1275e61b737.jpg</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>61</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Introducing our New European and American Style High-Waist Striped Drop-Seat Wide Leg Pants, designed for comfort and versatility. Perfect for the office or casual outings, these loose, straight-fit pants blend fashion with function. Enjoy effortless style and freedom of movement in this chic wardrobe essential that complements any look.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Bottoms , Wide Leg Pants</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>10</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>[['Dark blue-S', 'CJKT288836401AZ'], ['Dark blue-M', 'CJKT288836402BY'], ['Dark blue-L', 'CJKT288836403CX'], ['Dark blue-XL', 'CJKT288836404DW'], ['Dark blue-2XL', 'CJKT288836405EV'], ['Dark blue-3XL', 'CJKT288836406FU'], ['Black-S', 'CJKT288836407GT'], ['Black-M', 'CJKT288836408HS'], ['Black-L', 'CJKT288836409IR'], ['Black-XL', 'CJKT288836410JQ'], ['Black-2XL', 'CJKT288836411KP'], ['Black-3XL', 'CJKT288836412LO']]</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>280</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>CJKT2888364</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>2054509092887232513</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>nrsjefbcln5toii8v7yfer4x</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Resort-Style Linen Maxi Dress</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/cecdc928-4ff6-4dd4-9ffa-b9fe52007637.png,https://cf.cjdropshipping.com/3f39a222-9475-4984-b6d0-d1a26056b885.png,https://cf.cjdropshipping.com/39027d1b-b036-4c61-b604-72db23207053.png,https://cf.cjdropshipping.com/5a4ba703-beda-4571-bc0d-27892a583477.png</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Embrace effortless elegance with our Resort-Style Linen Maxi Dress. Perfect for sun-soaked days and balmy evenings, this stunning piece offers lightweight comfort and a relaxed silhouette. The breathable fabric flows beautifully, while its chic design ensures you stand out wherever your adventures take you. Step into style this season!</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>10</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>[['Navy Blue-S', 'CJLY288047701AZ'], ['Navy Blue-M', 'CJLY288047702BY'], ['Navy Blue-L', 'CJLY288047703CX'], ['Navy Blue-XL', 'CJLY288047704DW'], ['Navy Blue-XXL', 'CJLY288047705EV'], ['Pink-S', 'CJLY288047706FU'], ['Pink-M', 'CJLY288047707GT'], ['Pink-L', 'CJLY288047708HS'], ['Pink-XL', 'CJLY288047709IR'], ['Pink-XXL', 'CJLY288047710JQ'], ['Beige-S', 'CJLY288047711KP'], ['Beige-M', 'CJLY288047712LO'], ['Beige-L', 'CJLY288047713MN'], ['Beige-XL', 'CJLY288047714NM'], ['Beige-XXL', 'CJLY288047715OL'], ['Light  Blue-S', 'CJLY288047716PK'], ['Light  Blue-M', 'CJLY288047717QJ'], ['Light  Blue-L', 'CJLY288047718RI'], ['Light  Blue-XL', 'CJLY288047719SH'], ['Light  Blue-XXL', 'CJLY288047720TG']]</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>354</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>CJLY2880477</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>2054045654574039042</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1maommzfqzc86u9e7yaf3pw7</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Resort-Style Straight Mini Dress</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/07af67d8-3e8b-4484-baeb-bb4fb02de2c1.png,https://cf.cjdropshipping.com/c9339063-1fe7-40ee-b641-e8c17c93e676.png,https://cf.cjdropshipping.com/54507bdb-c07b-41b3-8daf-74e1b3f487ea.png,https://cf.cjdropshipping.com/c1fccc6d-8f98-4d1d-890d-3f6acedfd106.png,https://cf.cjdropshipping.com/0e7ab459-28f3-4cab-bf94-b886f0eca10e.png</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Experience effortless style with our Resort-Style Straight Mini Dress. Crafted for comfort and flair, this dress features a flattering silhouette perfect for any occasion. Embrace vibrant colors and chic designs that transition seamlessly from beach days to evening outings. Boost your wardrobe with this must-have piece that embodies relaxation and sophistication.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>[['Orange-S', 'CJLY288170401AZ'], ['Orange-M', 'CJLY288170402BY'], ['Orange-L', 'CJLY288170403CX'], ['Orange-XL', 'CJLY288170404DW'], ['Orange-XXL', 'CJLY288170405EV'], ['Yellow-S', 'CJLY288170406FU'], ['Yellow-M', 'CJLY288170407GT'], ['Yellow-L', 'CJLY288170408HS'], ['Yellow-XL', 'CJLY288170409IR'], ['Yellow-XXL', 'CJLY288170410JQ'], ['Blue-S', 'CJLY288170411KP'], ['Blue-M', 'CJLY288170412LO'], ['Blue-L', 'CJLY288170413MN'], ['Blue-XL', 'CJLY288170414NM'], ['Blue-XXL', 'CJLY288170415OL'], ['Green-S', 'CJLY288170416PK'], ['Green-M', 'CJLY288170417QJ'], ['Green-L', 'CJLY288170418RI'], ['Green-XL', 'CJLY288170419SH'], ['Green-XXL', 'CJLY288170420TG'], ['Pink-S', 'CJLY288170421UF'], ['Pink-M', 'CJLY288170422VE'], ['Pink-L', 'CJLY288170423WD'], ['Pink-XL', 'CJLY288170424XC'], ['Pink-XXL', 'CJLY288170425YB']]</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>219</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>CJLY2881704</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>2054096257990541314</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>avv7cjjnnq4qkwql0ueqnhft</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Square Neck Drop Shoulder Elastic Waist Romper</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/d7d6a65a-486f-46e5-abf6-7647a36f18c2.png,https://cf.cjdropshipping.com/661d5a7b-2b28-4a5b-9d9c-a4356d61c263.png,https://cf.cjdropshipping.com/341fe049-c5fe-43f5-af48-a24e159a8286.png</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Discover ultimate comfort and style with our Square Neck Drop Shoulder Elastic Waist Romper. This chic piece effortlessly combines casual and trendy vibes, featuring a flattering square neckline and relaxed drop shoulders. Perfect for any occasion, its elastic waist ensures a tailored fit while providing ease of movement. Embrace effortless fashion today!</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Rompers</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>[['Yellow-S', 'CJLT288190101AZ'], ['Yellow-M', 'CJLT288190102BY'], ['Yellow-L', 'CJLT288190103CX'], ['Yellow-XL', 'CJLT288190104DW'], ['Yellow-XXL', 'CJLT288190105EV'], ['Caramel-S', 'CJLT288190106FU'], ['Caramel-M', 'CJLT288190107GT'], ['Caramel-L', 'CJLT288190108HS'], ['Caramel-XL', 'CJLT288190109IR'], ['Caramel-XXL', 'CJLT288190110JQ'], ['Olive Green-S', 'CJLT288190111KP'], ['Olive Green-M', 'CJLT288190112LO'], ['Olive Green-L', 'CJLT288190113MN'], ['Olive Green-XL', 'CJLT288190114NM'], ['Olive Green-XXL', 'CJLT288190115OL']]</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>299</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>CJLT2881901</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>2054100409552371713</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>iz7oy7lhysw4kocsal02hma0</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Sexy Sheer Mesh Tie Lace Slip Dress 2018</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/2908e4d2-4c8c-4e6c-a18e-5e0e6d2e647b.jpg,https://cf.cjdropshipping.com/72d9a2de-e780-4e0b-8174-d8fd9283d8cf.jpg,https://cf.cjdropshipping.com/29b32c7c-1b09-4e43-ae55-8b8514d3c603.jpg,https://cf.cjdropshipping.com/eb6f9110-ff3c-4740-bbb1-00787ed1c67c.jpg,https://cf.cjdropshipping.com/67e88207-c446-4688-8c33-03f7ff8aa018.jpg</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>52</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Immerse yourself in allure with our Sexy Sheer Mesh Tie Lace Slip Dress. This stunning piece combines delicate transparency with enchanting lace details, creating a captivating silhouette. Perfect for romantic evenings or intimate gatherings, this dress beautifully embraces your curves while offering unparalleled comfort. Dare to shine and ignite passion!</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Intimates</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>[['S-White', 'CJQQ288273701AZ'], ['S-Black', 'CJQQ288273702BY'], ['M-White', 'CJQQ288273703CX'], ['M-Black', 'CJQQ288273704DW'], ['L-White', 'CJQQ288273705EV'], ['L-Black', 'CJQQ288273706FU'], ['XL-White', 'CJQQ288273707GT'], ['XL-Black', 'CJQQ288273708HS']]</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>70</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>CJQQ2882737</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>2054118975020392450</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>dnx5iiwrztbyjur10eypldmm</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>American Retro Flare Pants</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/5275d25f-da9f-42a0-8b06-767f274212c1.png,https://cf.cjdropshipping.com/b710425c-86b9-4c40-8b2d-8342167722e5.png</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Step into a vibrant era with our American Retro Flare Pants! Designed for ultimate comfort and style, these pants boast a chic, nostalgic silhouette. Perfect for casual outings or bold statements, they effortlessly blend vintage charm with modern flair. Embrace your individuality and showcase your style with every step!</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Bottoms , Wide Leg Pants</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>2</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>[['Brown  Orange-S', 'CJKT287539501AZ'], ['Brown  Orange-M', 'CJKT287539502BY'], ['Brown  Orange-L', 'CJKT287539503CX'], ['Brown  Orange-XL', 'CJKT287539504DW'], ['Brown  Orange-XXL', 'CJKT287539505EV'], ['Black  Gold-S', 'CJKT287539506FU'], ['Black  Gold-M', 'CJKT287539507GT'], ['Black  Gold-L', 'CJKT287539508HS'], ['Black  Gold-XL', 'CJKT287539509IR'], ['Black  Gold-XXL', 'CJKT287539510JQ']]</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>238</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>CJKT2875395</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>2052963169134497794</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>5znmlwu3cygrj5k0kh3p44os</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Bohemian Off-the-Shoulder Set</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/7bc4d735-f3dd-460b-9573-6ad75a4ba82e.png,https://cf.cjdropshipping.com/925dc8fc-7f7e-41e1-87c6-05f307f7f990.png</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Bohemian Off-the-Shoulder Set
+Embrace effortless style with our Bohemian Off-the-Shoulder Set. Featuring a relaxed silhouette and vibrant patterns, this chic ensemble is perfect for beach outings or brunch dates. The flowing fabric offers comfort, while the trendy design ensures you stand out. Add this stylish piece to your wardrobe today!</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>[['White Chevron-S', 'CJTZ287443901AZ'], ['White Chevron-M', 'CJTZ287443902BY'], ['White Chevron-L', 'CJTZ287443903CX'], ['White Chevron-XL', 'CJTZ287443904DW'], ['White Chevron-XXL', 'CJTZ287443905EV'], ['White Leafy-S', 'CJTZ287443906FU'], ['White Leafy-M', 'CJTZ287443907GT'], ['White Leafy-L', 'CJTZ287443908HS'], ['White Leafy-XL', 'CJTZ287443909IR'], ['White Leafy-XXL', 'CJTZ287443910JQ']]</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>359</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>CJTZ2874439</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>2052628466170499074</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>54stnn3jywaj78mj55o1mln5</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>White High-Waisted Wide Waistband Pleated A-Line Mini Skirt</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/6ec7694c-fbfa-49fe-af70-2d99b2b5fa3c.png,https://cf.cjdropshipping.com/3d631a53-b79d-4acf-bb49-0cce1167610a.png</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Upgrade your wardrobe with this stunning White High-Waisted Wide Waistband Pleated A-Line Mini Skirt. Its flattering silhouette and chic pleats create a perfect balance of elegance and style. Dress it up or down for any occasion, ensuring you stand out effortlessly. Experience comfort and fashion in one stylish piece!</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Bottoms , Skirts</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>4</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>[['White-S', 'CJQZ287469001AZ'], ['White-M', 'CJQZ287469002BY'], ['White-L', 'CJQZ287469003CX'], ['White-XL', 'CJQZ287469004DW'], ['White-XXL', 'CJQZ287469005EV'], ['Black-S', 'CJQZ287469006FU'], ['Black-M', 'CJQZ287469007GT'], ['Black-L', 'CJQZ287469008HS'], ['Black-XL', 'CJQZ287469009IR'], ['Black-XXL', 'CJQZ287469010JQ']]</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>179</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>CJQZ2874690</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>2052657062562017281</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>g0bwt0xxvl83xgtdparnhexc</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Women Autumn Elegant Sexy Solid Color Irregular Ruffle Dress With Belt</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/82a35abe-8c44-418b-90af-befb6f1d5114.jpg,https://cf.cjdropshipping.com/90a2cfc5-cee4-464c-a116-5e2e0fdab640.jpg,https://cf.cjdropshipping.com/10c3788f-af8a-4124-9fcd-0ad3eee01e4b.jpg,https://cf.cjdropshipping.com/069106a2-516c-4e95-a3d5-c484762eacbf.jpg</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Step into autumn with our Women’s Elegant Sexy Solid Color Irregular Ruffle Dress, designed to accentuate your curves. Featuring a chic belt and graceful ruffles, this eye-catching piece effortlessly blends sophistication and sultry charm. Perfect for any occasion, it’s a must-have addition to your wardrobe! Embrace your style today!</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>9</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>[['Black-Xs', 'CJLY287388501AZ'], ['Black-S', 'CJLY287388502BY'], ['Black-M', 'CJLY287388503CX'], ['Black-L', 'CJLY287388504DW'], ['Black-XL', 'CJLY287388505EV'], ['Black-2XL', 'CJLY287388506FU'], ['Black-3XL', 'CJLY287388507GT'], ['Black-4XL', 'CJLY287388508HS'], ['Black-5XL', 'CJLY287388509IR'], ['Khaki-Xs', 'CJLY287388510JQ'], ['Khaki-S', 'CJLY287388511KP'], ['Khaki-M', 'CJLY287388512LO'], ['Khaki-L', 'CJLY287388513MN'], ['Khaki-XL', 'CJLY287388514NM'], ['Khaki-2XL', 'CJLY287388515OL'], ['Khaki-3XL', 'CJLY287388516PK'], ['Khaki-4XL', 'CJLY287388517QJ'], ['Khaki-5XL', 'CJLY287388518RI'], ['White-Xs', 'CJLY287388519SH'], ['White-S', 'CJLY287388520TG'], ['White-M', 'CJLY287388521UF'], ['White-L', 'CJLY287388522VE'], ['White-XL', 'CJLY287388523WD'], ['White-2XL', 'CJLY287388524XC'], ['White-3XL', 'CJLY287388525YB'], ['White-4XL', 'CJLY287388526ZA'], ['White-5XL', 'CJLY287388527AZ'], ['Navy Blue-Xs', 'CJLY287388528BY'], ['Navy Blue-S', 'CJLY287388529CX'], ['Navy Blue-M', 'CJLY287388530DW'], ['Navy Blue-L', 'CJLY287388531EV'], ['Navy Blue-XL', 'CJLY287388532FU'], ['Navy Blue-2XL', 'CJLY287388533GT'], ['Navy Blue-3XL', 'CJLY287388534HS'], ['Navy Blue-4XL', 'CJLY287388535IR'], ['Navy Blue-5XL', 'CJLY287388536JQ']]</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>449</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>CJLY2873885</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>2052577431829778434</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>c0smsoqfpc9xdco7jo6d50gf</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Fashion Urban Commute Bodycon Skirt And Top Two-Piece Set</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/2deca370-dd65-4629-9b2e-80d627d27638.jpg,https://cf.cjdropshipping.com/823605a1-8bce-4d59-b52d-2f1ab8ed2122.jpg,https://cf.cjdropshipping.com/7cf2b798-7d38-4e11-9694-9e3acf1b985a.jpg,https://cf.cjdropshipping.com/cfadaef0-2460-4985-8d7c-be824154f5a7.jpg,https://cf.cjdropshipping.com/70063c6f-6a67-445b-9129-0e12c2716d25.jpg,https://cf.cjdropshipping.com/229b0fdd-cb1c-4d8a-acb0-374acf20f53d.jpg,https://cf.cjdropshipping.com/01053774-d76d-4860-be23-81552d54b974.jpg,https://cf.cjdropshipping.com/07f85b5c-1207-447a-808e-923a40f29018.jpg,https://cf.cjdropshipping.com/34ac54ea-1802-45c4-a994-6aca359f346d.jpg,https://cf.cjdropshipping.com/89fbba53-570c-4999-baaf-91f0823c9558.jpg</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Upgrade your wardrobe with the Fashion Urban Commute Bodycon Skirt and Top Two-Piece Set. This stylish ensemble combines form-fitting design with comfort, perfect for city adventures or casual outings. Effortlessly chic, it transitions from day to night. Flaunt your confidence and embrace modern fashion—your go-to outfit awaits!</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>16</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>[['Black-XS', 'CJLY287231001AZ'], ['Black-S', 'CJLY287231002BY'], ['Black-M', 'CJLY287231003CX'], ['Black-L', 'CJLY287231004DW'], ['Black-2XL', 'CJLY287231005EV'], ['Black-3XL', 'CJLY287231006FU'], ['Black-4XL', 'CJLY287231007GT'], ['Navy Blue-XS', 'CJLY287231008HS'], ['Navy Blue-S', 'CJLY287231009IR'], ['Navy Blue-M', 'CJLY287231010JQ'], ['Navy Blue-L', 'CJLY287231011KP'], ['Navy Blue-2XL', 'CJLY287231012LO'], ['Navy Blue-3XL', 'CJLY287231013MN'], ['Navy Blue-4XL', 'CJLY287231014NM'], ['White-XS', 'CJLY287231015OL'], ['White-S', 'CJLY287231016PK'], ['White-M', 'CJLY287231017QJ'], ['White-L', 'CJLY287231018RI'], ['White-2XL', 'CJLY287231019SH'], ['White-3XL', 'CJLY287231020TG'], ['White-4XL', 'CJLY287231021UF'], ['Beige-XS', 'CJLY287231022VE'], ['Beige-S', 'CJLY287231023WD'], ['Beige-M', 'CJLY287231024XC'], ['Beige-L', 'CJLY287231025YB'], ['Beige-2XL', 'CJLY287231026ZA'], ['Beige-3XL', 'CJLY287231027AZ'], ['Beige-4XL', 'CJLY287231028BY'], ['Royal Blue-XS', 'CJLY287231029CX'], ['Royal Blue-S', 'CJLY287231030DW'], ['Royal Blue-M', 'CJLY287231031EV'], ['Royal Blue-L', 'CJLY287231032FU'], ['Royal Blue-2XL', 'CJLY287231033GT'], ['Royal Blue-3XL', 'CJLY287231034HS'], ['Royal Blue-4XL', 'CJLY287231035IR'], ['Burgundy-XS', 'CJLY287231036JQ'], ['Burgundy-S', 'CJLY287231037KP'], ['Burgundy-M', 'CJLY287231038LO'], ['Burgundy-L', 'CJLY287231039MN'], ['Burgundy-2XL', 'CJLY287231040NM'], ['Burgundy-3XL', 'CJLY287231041OL'], ['Burgundy-4XL', 'CJLY287231042PK'], ['Dark Green-XS', 'CJLY287231043QJ'], ['Dark Green-S', 'CJLY287231044RI'], ['Dark Green-M', 'CJLY287231045SH'], ['Dark Green-L', 'CJLY287231046TG'], ['Dark Green-2XL', 'CJLY287231047UF'], ['Dark Green-3XL', 'CJLY287231048VE'], ['Dark Green-4XL', 'CJLY287231049WD'], ['Purple-XS', 'CJLY287231050XC'], ['Purple-S', 'CJLY287231051YB'], ['Purple-M', 'CJLY287231052ZA'], ['Purple-L', 'CJLY287231053AZ'], ['Purple-2XL', 'CJLY287231054BY'], ['Purple-3XL', 'CJLY287231055CX'], ['Purple-4XL', 'CJLY287231056DW'], ['Pink-XS', 'CJLY287231057EV'], ['Pink-S', 'CJLY287231058FU'], ['Pink-M', 'CJLY287231059GT'], ['Pink-L', 'CJLY287231060HS'], ['Pink-2XL', 'CJLY287231061IR'], ['Pink-3XL', 'CJLY287231062JQ'], ['Pink-4XL', 'CJLY287231063KP'], ['Light Blue-XS', 'CJLY287231064LO'], ['Light Blue-S', 'CJLY287231065MN'], ['Light Blue-M', 'CJLY287231066NM'], ['Light Blue-L', 'CJLY287231067OL'], ['Light Blue-2XL', 'CJLY287231068PK'], ['Light Blue-3XL', 'CJLY287231069QJ'], ['Light Blue-4XL', 'CJLY287231070RI'], ['Black-Xl', 'CJLY287231071SH'], ['Navy Blue-Xl', 'CJLY287231072TG'], ['White-Xl', 'CJLY287231073UF'], ['Beige-Xl', 'CJLY287231074VE'], ['Royal Blue-Xl', 'CJLY287231075WD'], ['Burgundy-Xl', 'CJLY287231076XC'], ['Dark Green-Xl', 'CJLY287231077YB'], ['Purple-Xl', 'CJLY287231078ZA'], ['Pink-Xl', 'CJLY287231079AZ'], ['Light Blue-Xl', 'CJLY287231080BY']]</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>500</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>1</v>
+      </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>CJLY2872310</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>2052223681996099585</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>31gr2dyw3srcof7w97k04ujr</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Japanese Linen-Blend Kimono-Style Cardigan</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/d0861f1d-32ff-463f-968d-d06a95eab52b.png,https://cf.cjdropshipping.com/3090e5bf-2d38-4ecc-b7ec-ddc4320b4777.png,https://cf.cjdropshipping.com/d70142d3-8b0f-4a53-9be1-7e1733aa3ee7.png,https://cf.cjdropshipping.com/a26757ab-aaad-4416-b5d5-cd3e7b593094.png,https://cf.cjdropshipping.com/2b30cfc2-ad86-4be2-9240-3067d8850938.png</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Introducing the Japanese Linen-Blend Kimono-Style Cardigan, a perfect fusion of elegance and comfort. Crafted from a luxurious linen blend, this lightweight cardigan features a stylish open front and flowing sleeves, making it ideal for layering. Elevate your wardrobe with this versatile piece that seamlessly transitions from day to night.</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Outerwear , Jackets , Blazers</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>13</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>[['Lime Green-S', 'CJQB287218901AZ'], ['Lime Green-M', 'CJQB287218902BY'], ['Lime Green-L', 'CJQB287218903CX'], ['Lime Green-XL', 'CJQB287218904DW'], ['Lime Green-XXL', 'CJQB287218905EV'], ['Khaki Brown-S', 'CJQB287218906FU'], ['Khaki Brown-M', 'CJQB287218907GT'], ['Khaki Brown-L', 'CJQB287218908HS'], ['Khaki Brown-XL', 'CJQB287218909IR'], ['Khaki Brown-XXL', 'CJQB287218910JQ'], ['Denim Blue-S', 'CJQB287218911KP'], ['Denim Blue-M', 'CJQB287218912LO'], ['Denim Blue-L', 'CJQB287218913MN'], ['Denim Blue-XL', 'CJQB287218914NM'], ['Denim Blue-XXL', 'CJQB287218915OL'], ['Heather Gray-S', 'CJQB287218916PK'], ['Heather Gray-M', 'CJQB287218917QJ'], ['Heather Gray-L', 'CJQB287218918RI'], ['Heather Gray-XL', 'CJQB287218919SH'], ['Heather Gray-XXL', 'CJQB287218920TG'], ['OffWhite-S', 'CJQB287218921UF'], ['OffWhite-M', 'CJQB287218922VE'], ['OffWhite-L', 'CJQB287218923WD'], ['OffWhite-XL', 'CJQB287218924XC'], ['OffWhite-XXL', 'CJQB287218925YB']]</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>300</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>CJQB2872189</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>2052207717179846657</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>df2aaiaqrdmu5elcr5s1i7xx</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Women's Knitted Long And Micro Flared Side Pocket Pants</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/77d857b8-4e84-4262-9658-034027e49234.jpg,https://cf.cjdropshipping.com/4238e163-94e9-4e22-89fb-97457cb89398.jpg,https://cf.cjdropshipping.com/cad5ccff-086c-4701-a3a2-fd98ccab5a24.png,https://cf.cjdropshipping.com/ed053fec-6faf-4862-860d-f26e06a0277f.jpg,https://cf.cjdropshipping.com/2dd45afb-ec44-4bdb-80cd-3e6aab7bd40f.jpg</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Experience ultimate comfort with our Women's Knitted Long and Micro Flared Side Pocket Pants. These stylish bottoms feature a relaxed fit, perfect for both lounging and casual outings. The side pockets add practicality without sacrificing elegance. Make a fashion statement while enjoying all-day ease and versatility in your wardrobe today!</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Bottoms , Wide Leg Pants</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>11</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>[['S-Black', 'CJKT287137201AZ'], ['S-Apricot color', 'CJKT287137202BY'], ['S-Dark blue', 'CJKT287137203CX'], ['S-Gray', 'CJKT287137204DW'], ['M-Black', 'CJKT287137205EV'], ['M-Apricot color', 'CJKT287137206FU'], ['M-Dark blue', 'CJKT287137207GT'], ['M-Gray', 'CJKT287137208HS'], ['L-Black', 'CJKT287137209IR'], ['L-Apricot color', 'CJKT287137210JQ'], ['L-Dark blue', 'CJKT287137211KP'], ['L-Gray', 'CJKT287137212LO'], ['XL-Black', 'CJKT287137213MN'], ['XL-Apricot color', 'CJKT287137214NM'], ['XL-Dark blue', 'CJKT287137215OL'], ['XL-Gray', 'CJKT287137216PK'], ['2XL-Black', 'CJKT287137217QJ'], ['2XL-Apricot color', 'CJKT287137218RI'], ['2XL-Dark blue', 'CJKT287137219SH'], ['2XL-Gray', 'CJKT287137220TG'], ['S-Dark gray', 'CJKT287137221UF'], ['M-Dark gray', 'CJKT287137222VE'], ['L-Dark gray', 'CJKT287137223WD'], ['XL-Dark gray', 'CJKT287137224XC'], ['2XL-Dark gray', 'CJKT287137225YB']]</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>250</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>CJKT2871372</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>2051920489276395521</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>f2zg6ugxakjebpx011a51dqk</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026 New Polo V-neck Bubble Sleeve Loose Shirt Dress</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/95c2171c-db38-4625-8ed0-01026c6abea9.png,https://cf.cjdropshipping.com/395f22ea-122e-4283-b937-085d68af2c3b.png,https://cf.cjdropshipping.com/47de6aff-2b5a-402f-a1f0-1361ccd43624.png</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Introducing the 2026 New Polo V-neck Bubble Sleeve Loose Shirt Dress, a perfect blend of comfort and style. Crafted for modern elegance, this dress features a chic V-neck design and playful bubble sleeves. Effortlessly elevate your wardrobe with its relaxed fit, making it ideal for casual outings or brunch dates.</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>24</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>[['Apricot-S', 'CJLY287187501AZ'], ['Apricot-M', 'CJLY287187502BY'], ['Apricot-L', 'CJLY287187503CX'], ['Apricot-Xl', 'CJLY287187504DW'], ['Apricot-Xxl', 'CJLY287187505EV'], ['Black-S', 'CJLY287187506FU'], ['Black-M', 'CJLY287187507GT'], ['Black-L', 'CJLY287187508HS'], ['Black-Xl', 'CJLY287187509IR'], ['Black-Xxl', 'CJLY287187510JQ'], ['Brown-S', 'CJLY287187511KP'], ['Brown-M', 'CJLY287187512LO'], ['Brown-L', 'CJLY287187513MN'], ['Brown-Xl', 'CJLY287187514NM'], ['Brown-Xxl', 'CJLY287187515OL']]</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>320</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>CJLY2871875</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>2051961966674329601</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>imc2yspxbq8agoy7gveq95wl</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026 New Ruffle Loose Middle Sleeve Dress</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/e4b25d81-bf4d-4bbf-8cfd-ccd3b93114a0.png,https://cf.cjdropshipping.com/17a120ce-846e-40ff-85e1-74dc5b9976d0.png</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Introducing the 2026 New Ruffle Loose Middle Sleeve Dress, a perfect blend of comfort and style. With its flowing silhouette and chic ruffle details, this dress enhances every figure. Dress it up or keep it casual—ideal for any occasion. Embrace effortless elegance and turn heads wherever you go!</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>14</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>[['Green-S', 'CJLY286907001AZ'], ['Green-M', 'CJLY286907002BY'], ['Green-L', 'CJLY286907003CX'], ['Green-Xl', 'CJLY286907004DW'], ['Green-Xxl', 'CJLY286907005EV']]</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>300</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>1</v>
+      </c>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>CJLY2869070</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>2051491858033041410</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>psw78rckpnrr7e1n0fj170zy</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Solid Color Long Sleeve Blazer Collar Single-Breasted Fitted Long Blazer Dress</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/65a43e5b-0c92-472b-82d5-f94055374b50.jpg,https://cf.cjdropshipping.com/a2e09398-d6b7-4df6-a295-b4b5955bf918.jpg,https://cf.cjdropshipping.com/2912c8d1-6815-469f-bc48-001b10445d9e.jpg,https://cf.cjdropshipping.com/4e632d69-86a1-4ce0-b0bb-409fe0fdf80d.jpg,https://cf.cjdropshipping.com/2ca4a0bd-c047-4116-8c09-07ff56a36839.jpg</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Elevate your wardrobe with the Solid Color Long Sleeve Blazer. This chic, fitted blazer dress features a sophisticated collar and single-breasted design, perfect for both professional settings and stylish outings. Versatile and timeless, it effortlessly enhances any ensemble, providing a polished look that commands attention wherever you go. Experience true elegance!</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>17</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>[['White-XS', 'CJLY286814501AZ'], ['White-S', 'CJLY286814502BY'], ['White-M', 'CJLY286814503CX'], ['White-L', 'CJLY286814504DW'], ['White-XL', 'CJLY286814505EV'], ['White-2XL', 'CJLY286814506FU'], ['White-3XL', 'CJLY286814507GT'], ['White-4XL', 'CJLY286814508HS'], ['Navy Blue-XS', 'CJLY286814509IR'], ['Navy Blue-S', 'CJLY286814510JQ'], ['Navy Blue-M', 'CJLY286814511KP'], ['Navy Blue-L', 'CJLY286814512LO'], ['Navy Blue-XL', 'CJLY286814513MN'], ['Navy Blue-2XL', 'CJLY286814514NM'], ['Navy Blue-3XL', 'CJLY286814515OL'], ['Navy Blue-4XL', 'CJLY286814516PK'], ['Black-XS', 'CJLY286814517QJ'], ['Black-S', 'CJLY286814518RI'], ['Black-M', 'CJLY286814519SH'], ['Black-L', 'CJLY286814520TG'], ['Black-XL', 'CJLY286814521UF'], ['Black-2XL', 'CJLY286814522VE'], ['Black-3XL', 'CJLY286814523WD'], ['Black-4XL', 'CJLY286814524XC'], ['Burgundy-XS', 'CJLY286814525YB'], ['Burgundy-S', 'CJLY286814526ZA'], ['Burgundy-M', 'CJLY286814527AZ'], ['Burgundy-L', 'CJLY286814528BY'], ['Burgundy-XL', 'CJLY286814529CX'], ['Burgundy-2XL', 'CJLY286814530DW'], ['Burgundy-3XL', 'CJLY286814531EV'], ['Burgundy-4XL', 'CJLY286814532FU'], ['Dark Grey-XS', 'CJLY286814533GT'], ['Dark Grey-S', 'CJLY286814534HS'], ['Dark Grey-M', 'CJLY286814535IR'], ['Dark Grey-L', 'CJLY286814536JQ'], ['Dark Grey-XL', 'CJLY286814537KP'], ['Dark Grey-2XL', 'CJLY286814538LO'], ['Dark Grey-3XL', 'CJLY286814539MN'], ['Dark Grey-4XL', 'CJLY286814540NM']]</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>500</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>CJLY2868145</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>2051188459355877377</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>5vhgdogfkknarw2ur9jb99so</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Collared Button-Front Fitted Bodycon Short-Sleeve Dress</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/6e06e9f0-adfe-452e-ad59-8f6725972f8b.png,https://cf.cjdropshipping.com/cb4dcea3-7dd0-4657-9fe8-bf194c2ab9eb.png,https://cf.cjdropshipping.com/7c021788-7983-4856-a0fa-f9f0fbdb5023.png</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Step into style with our Collared Button-Front Fitted Bodycon Short-Sleeve Dress. This chic piece accentuates your figure, offering a modern twist on classic fashion. Perfect for any occasion, it combines comfort and sophistication, making it a must-have addition to your wardrobe. Unleash your confidence and turn heads effortlessly!</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Lady Dresses</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>12</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>[['Heather Grey-S', 'CJLY286405501AZ'], ['Heather Grey-M', 'CJLY286405502BY'], ['Heather Grey-L', 'CJLY286405503CX'], ['Heather Grey-XL', 'CJLY286405504DW'], ['Heather Grey-XXL', 'CJLY286405505EV'], ['Daisy Print-S', 'CJLY286405506FU'], ['Daisy Print-M', 'CJLY286405507GT'], ['Daisy Print-L', 'CJLY286405508HS'], ['Daisy Print-XL', 'CJLY286405509IR'], ['Daisy Print-XXL', 'CJLY286405510JQ'], ['Brown  White-S', 'CJLY286405511KP'], ['Brown  White-M', 'CJLY286405512LO'], ['Brown  White-L', 'CJLY286405513MN'], ['Brown  White-XL', 'CJLY286405514NM'], ['Brown  White-XXL', 'CJLY286405515OL']]</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>318</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>CJLY2864055</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>2049785700151775233</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>mk4a4pnow8fnjt0my273siu0</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Low-Rise Flare Pants</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/4702e1d0-fce0-417d-9cbf-0655a82624d1.png,https://cf.cjdropshipping.com/433dae25-9aab-44b8-b7a7-9f028805afcb.png,https://cf.cjdropshipping.com/5c8fbcb2-71b3-44d0-92c3-cc349d1dc8ac.png</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Revamp your wardrobe with our chic Low-Rise Flare Pants, designed for ultimate comfort and style. Featuring a flattering fit that highlights your curves, these versatile bottoms are perfect for any occasion. Dress them up or down, and enjoy the perfect blend of sophistication and casual cool every day!</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Bottoms , Wide Leg Pants</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>[['Retro-S', 'CJKT286292001AZ'], ['Retro-M', 'CJKT286292002BY'], ['Retro-L', 'CJKT286292003CX'], ['Retro-XL', 'CJKT286292004DW'], ['Retro-XXL', 'CJKT286292005EV'], ['Purple-S', 'CJKT286292006FU'], ['Purple-M', 'CJKT286292007GT'], ['Purple-L', 'CJKT286292008HS'], ['Purple-XL', 'CJKT286292009IR'], ['Purple-XXL', 'CJKT286292010JQ'], ['Brown-S', 'CJKT286292011KP'], ['Brown-M', 'CJKT286292012LO'], ['Brown-L', 'CJKT286292013MN'], ['Brown-XL', 'CJKT286292014NM'], ['Brown-XXL', 'CJKT286292015OL'], ['Retro-XS', 'CJKT286292016PK'], ['Purple-XS', 'CJKT286292017QJ'], ['Brown-XS', 'CJKT286292018RI']]</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>306</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>CJKT2862920</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>2049691796840697857</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>wl2spmtutum3gcaumtlpsots</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026 V-neck Sleeveless Workwear Style Jumpsuit</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/b2c8c726-04a0-42a7-bc1c-21e548f06ff8.png,https://oss-cf.cjdropshipping.com/product/2026/06/01/02/cc8a7426-5351-4fb5-94a5-af08cf669d81.jpg</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>77</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Step into sophistication with the 2026 V-neck Sleeveless Workwear Style Jumpsuit. This chic jumpsuit combines comfort and professionalism, offering a flattering silhouette for the modern influencer. Perfect for meetings or casual outings, it transitions seamlessly from day to night while exuding timeless elegance. Make a statement wherever you go!</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Rompers</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>8</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>[['Dark blue-S', 'CJLT286390601AZ'], ['Dark blue-M', 'CJLT286390602BY'], ['Dark blue-L', 'CJLT286390603CX'], ['Dark blue-Xl', 'CJLT286390604DW'], ['Dark blue-Xxl', 'CJLT286390605EV'], ['Green-S', 'CJLT286390606FU'], ['Green-M', 'CJLT286390607GT'], ['Green-L', 'CJLT286390608HS'], ['Green-Xl', 'CJLT286390609IR'], ['Green-Xxl', 'CJLT286390610JQ']]</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>465</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>CJLT2863906</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>2049760984099770369</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ck59gdrjgp6pkcxsq0vbuw8v</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>676716d67602c42f64f06f94</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Satin High-Neck Asymmetric Waist Wide-Leg Pants Set</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://cf.cjdropshipping.com/9f0154cf-b4be-44cf-ad6a-bd1e88b9a3e6.png,https://cf.cjdropshipping.com/9adae95b-4184-429e-a106-329755bebc08.png,https://cf.cjdropshipping.com/f0c1d576-6587-4c28-bf1b-b0d49b69a98a.png</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Step into sophistication with our Satin High-Neck Asymmetric Waist Wide-Leg Pants Set. This stunning ensemble features flowing wide-leg pants paired with a chic high-neck top, creating an effortlessly glamorous silhouette. Perfect for both casual outings and upscale events, this versatile outfit will surely make a striking fashion statement wherever you go!</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>womens</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Women's Clothing , Tops , Sets , Suits , Sets</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>6</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>[['Caramel-S', 'CJTZ285996201AZ'], ['Caramel-M', 'CJTZ285996202BY'], ['Caramel-L', 'CJTZ285996203CX'], ['Caramel-XL', 'CJTZ285996204DW'], ['Caramel-XXL', 'CJTZ285996205EV'], ['Klein Blue-S', 'CJTZ285996206FU'], ['Klein Blue-M', 'CJTZ285996207GT'], ['Klein Blue-L', 'CJTZ285996208HS'], ['Klein Blue-XL', 'CJTZ285996209IR'], ['Klein Blue-XXL', 'CJTZ285996210JQ'], ['OffWhite-S', 'CJTZ285996211KP'], ['OffWhite-M', 'CJTZ285996212LO'], ['OffWhite-L', 'CJTZ285996213MN'], ['OffWhite-XL', 'CJTZ285996214NM'], ['OffWhite-XXL', 'CJTZ285996215OL']]</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>380</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>CJTZ2859962</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>2049392126572232706</t>
         </is>
       </c>
     </row>
